--- a/database/event/2573/event_2573_evp_summary.xlsx
+++ b/database/event/2573/event_2573_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.244</v>
+        <v>7.9942</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8752</v>
+        <v>0.9659</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5051</v>
+        <v>2.741</v>
       </c>
       <c r="E2" t="n">
-        <v>7.244</v>
+        <v>7.9942</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5302</v>
+        <v>4.2804</v>
       </c>
       <c r="G2" t="n">
         <v>3.7138</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5302</v>
+        <v>4.6604</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8613</v>
+        <v>3.7774</v>
       </c>
       <c r="J2" t="n">
         <v>3.7138</v>
@@ -529,7 +529,7 @@
         <v>147</v>
       </c>
       <c r="M2" t="n">
-        <v>6.5751</v>
+        <v>7.4912</v>
       </c>
       <c r="N2" t="n">
         <v>184</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.6604</v>
+        <v>5.9194</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6839</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8653</v>
+        <v>1.9144</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6604</v>
+        <v>5.9194</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9734</v>
+        <v>2.2324</v>
       </c>
       <c r="G3" t="n">
         <v>3.687</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9734</v>
+        <v>2.2324</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5995</v>
+        <v>1.8094</v>
       </c>
       <c r="J3" t="n">
         <v>3.687</v>
@@ -575,7 +575,7 @@
         <v>147</v>
       </c>
       <c r="M3" t="n">
-        <v>5.2865</v>
+        <v>5.4964</v>
       </c>
       <c r="N3" t="n">
         <v>184</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.4911</v>
+        <v>5.5677</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6634</v>
+        <v>0.6727</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7969</v>
+        <v>1.7743</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4911</v>
+        <v>5.5677</v>
       </c>
       <c r="F4" t="n">
-        <v>4.3211</v>
+        <v>4.3977</v>
       </c>
       <c r="G4" t="n">
         <v>1.17</v>
       </c>
       <c r="H4" t="n">
-        <v>4.8242</v>
+        <v>5.1325</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9102</v>
+        <v>4.1601</v>
       </c>
       <c r="J4" t="n">
         <v>1.17</v>
@@ -621,7 +621,7 @@
         <v>96</v>
       </c>
       <c r="M4" t="n">
-        <v>5.0802</v>
+        <v>5.3301</v>
       </c>
       <c r="N4" t="n">
         <v>180</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5146</v>
+        <v>5.2801</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5455</v>
+        <v>0.6379</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4024</v>
+        <v>1.6597</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5146</v>
+        <v>5.2801</v>
       </c>
       <c r="F5" t="n">
-        <v>4.2254</v>
+        <v>3.8197</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2892</v>
+        <v>1.4604</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4392</v>
+        <v>3.8197</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5981</v>
+        <v>3.0959</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2892</v>
+        <v>1.4604</v>
       </c>
       <c r="K5" t="n">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="L5" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8873</v>
+        <v>4.5563</v>
       </c>
       <c r="N5" t="n">
-        <v>180</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3115</v>
+        <v>4.6106</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5209</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3204</v>
+        <v>1.393</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3115</v>
+        <v>4.6106</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8511</v>
+        <v>4.3214</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4604</v>
+        <v>0.2892</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8511</v>
+        <v>4.8256</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3109</v>
+        <v>3.9113</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4604</v>
+        <v>0.2892</v>
       </c>
       <c r="K6" t="n">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="L6" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7713</v>
+        <v>4.2005</v>
       </c>
       <c r="N6" t="n">
-        <v>155</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7">
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3614</v>
+        <v>3.3623</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4061</v>
+        <v>0.4062</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9366</v>
+        <v>0.8956</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3614</v>
+        <v>3.3623</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7197</v>
+        <v>0.7206</v>
       </c>
       <c r="G7" t="n">
         <v>2.6417</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7197</v>
+        <v>0.7206</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5834</v>
+        <v>0.5841</v>
       </c>
       <c r="J7" t="n">
         <v>2.6417</v>
@@ -759,7 +759,7 @@
         <v>147</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2251</v>
+        <v>3.2258</v>
       </c>
       <c r="N7" t="n">
         <v>184</v>
@@ -768,47 +768,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.52</v>
+        <v>3.0096</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3045</v>
+        <v>0.3636</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5967</v>
+        <v>0.7551</v>
       </c>
       <c r="E8" t="n">
-        <v>2.52</v>
+        <v>3.0096</v>
       </c>
       <c r="F8" t="n">
-        <v>3.167</v>
+        <v>3.3605</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.647</v>
+        <v>-0.3509</v>
       </c>
       <c r="H8" t="n">
-        <v>3.167</v>
+        <v>3.3605</v>
       </c>
       <c r="I8" t="n">
-        <v>2.567</v>
+        <v>2.7238</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.647</v>
+        <v>-0.3509</v>
       </c>
       <c r="K8" t="n">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="L8" t="n">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="M8" t="n">
-        <v>1.92</v>
+        <v>2.3729</v>
       </c>
       <c r="N8" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9">
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3535</v>
+        <v>2.9115</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2843</v>
+        <v>0.3518</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5294</v>
+        <v>0.716</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3535</v>
+        <v>2.9115</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7561</v>
+        <v>3.3141</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4026</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7561</v>
+        <v>3.3141</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2339</v>
+        <v>2.6862</v>
       </c>
       <c r="J9" t="n">
         <v>-0.4026</v>
@@ -851,7 +851,7 @@
         <v>96</v>
       </c>
       <c r="M9" t="n">
-        <v>1.8313</v>
+        <v>2.2836</v>
       </c>
       <c r="N9" t="n">
         <v>180</v>
@@ -860,185 +860,185 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rickeh</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3383</v>
+        <v>2.6344</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2825</v>
+        <v>0.3183</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5233</v>
+        <v>0.6056</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3383</v>
+        <v>2.6344</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3383</v>
+        <v>3.2814</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0.647</v>
       </c>
       <c r="H10" t="n">
-        <v>2.3383</v>
+        <v>3.2814</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3492</v>
+        <v>2.6597</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0.647</v>
       </c>
       <c r="K10" t="n">
-        <v>190</v>
+        <v>84</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3492</v>
+        <v>2.0127</v>
       </c>
       <c r="N10" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2725</v>
+        <v>2.6023</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2746</v>
+        <v>0.3144</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4967</v>
+        <v>0.5928</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2725</v>
+        <v>2.6023</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2725</v>
+        <v>1.8933</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.709</v>
       </c>
       <c r="H11" t="n">
-        <v>2.2725</v>
+        <v>1.8933</v>
       </c>
       <c r="I11" t="n">
-        <v>2.2831</v>
+        <v>1.5346</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.709</v>
       </c>
       <c r="K11" t="n">
-        <v>190</v>
+        <v>37</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="M11" t="n">
-        <v>2.2831</v>
+        <v>2.2436</v>
       </c>
       <c r="N11" t="n">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>Rickeh</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.2389</v>
+        <v>2.3296</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2705</v>
+        <v>0.2815</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4831</v>
+        <v>0.4842</v>
       </c>
       <c r="E12" t="n">
-        <v>2.2389</v>
+        <v>2.3296</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5898</v>
+        <v>2.3296</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3509</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5898</v>
+        <v>2.3296</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0991</v>
+        <v>2.3492</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3509</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>37</v>
+        <v>190</v>
       </c>
       <c r="L12" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.7482</v>
+        <v>2.3492</v>
       </c>
       <c r="N12" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2102</v>
+        <v>2.264</v>
       </c>
       <c r="C13" t="n">
-        <v>0.267</v>
+        <v>0.2735</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4715</v>
+        <v>0.4581</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2102</v>
+        <v>2.264</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5012</v>
+        <v>2.264</v>
       </c>
       <c r="G13" t="n">
-        <v>0.709</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5012</v>
+        <v>2.264</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2168</v>
+        <v>2.2831</v>
       </c>
       <c r="J13" t="n">
-        <v>0.709</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>37</v>
+        <v>190</v>
       </c>
       <c r="L13" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9258</v>
+        <v>2.2831</v>
       </c>
       <c r="N13" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1259</v>
+        <v>2.1752</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2568</v>
+        <v>0.2628</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4375</v>
+        <v>0.4227</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1259</v>
+        <v>2.1752</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0704</v>
+        <v>2.1197</v>
       </c>
       <c r="G14" t="n">
         <v>0.0555</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0704</v>
+        <v>2.1197</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6781</v>
+        <v>1.7181</v>
       </c>
       <c r="J14" t="n">
         <v>0.0555</v>
@@ -1081,7 +1081,7 @@
         <v>57</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7336</v>
+        <v>1.7736</v>
       </c>
       <c r="N14" t="n">
         <v>186</v>
@@ -1090,78 +1090,78 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7507</v>
+        <v>1.8818</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2115</v>
+        <v>0.2274</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2859</v>
+        <v>0.3058</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7507</v>
+        <v>1.8818</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7507</v>
+        <v>2.3879</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.5061</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7507</v>
+        <v>2.3879</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7588</v>
+        <v>1.9355</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.5061</v>
       </c>
       <c r="K15" t="n">
-        <v>190</v>
+        <v>129</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7588</v>
+        <v>1.4294</v>
       </c>
       <c r="N15" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7431</v>
+        <v>1.7441</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2106</v>
+        <v>0.2107</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2828</v>
+        <v>0.2509</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7431</v>
+        <v>1.7441</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7431</v>
+        <v>1.7441</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7431</v>
+        <v>1.7441</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7512</v>
+        <v>1.7588</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7512</v>
+        <v>1.7588</v>
       </c>
       <c r="N16" t="n">
         <v>190</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6051</v>
+        <v>1.7366</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1939</v>
+        <v>0.2098</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2271</v>
+        <v>0.248</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6051</v>
+        <v>1.7366</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1917</v>
+        <v>1.7366</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4134</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1917</v>
+        <v>1.7366</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9659</v>
+        <v>1.7512</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4134</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>47</v>
+        <v>190</v>
       </c>
       <c r="L17" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3793</v>
+        <v>1.7512</v>
       </c>
       <c r="N17" t="n">
-        <v>155</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6</v>
+        <v>1.7281</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1933</v>
+        <v>0.2088</v>
       </c>
       <c r="D18" t="n">
-        <v>0.225</v>
+        <v>0.2446</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6</v>
+        <v>1.7281</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1061</v>
+        <v>1.3147</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5061</v>
+        <v>0.4134</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1061</v>
+        <v>1.3147</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7071</v>
+        <v>1.0656</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5061</v>
+        <v>0.4134</v>
       </c>
       <c r="K18" t="n">
-        <v>129</v>
+        <v>47</v>
       </c>
       <c r="L18" t="n">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="M18" t="n">
-        <v>1.201</v>
+        <v>1.479</v>
       </c>
       <c r="N18" t="n">
-        <v>186</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19">
@@ -1284,7 +1284,7 @@
         <v>0.188</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2072</v>
+        <v>0.176</v>
       </c>
       <c r="E19" t="n">
         <v>1.556</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4007</v>
+        <v>1.4098</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1692</v>
+        <v>0.1703</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1445</v>
+        <v>0.1178</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4007</v>
+        <v>1.4098</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4944</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>0.9063</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4944</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4008</v>
+        <v>0.4081</v>
       </c>
       <c r="J20" t="n">
         <v>0.9063</v>
@@ -1357,7 +1357,7 @@
         <v>108</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3071</v>
+        <v>1.3144</v>
       </c>
       <c r="N20" t="n">
         <v>155</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1861</v>
+        <v>1.4073</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1433</v>
+        <v>0.17</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0578</v>
+        <v>0.1168</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1861</v>
+        <v>1.4073</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8713</v>
+        <v>2.0925</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6852</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8713</v>
+        <v>2.0925</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5167</v>
+        <v>1.696</v>
       </c>
       <c r="J21" t="n">
         <v>-0.6852</v>
@@ -1403,7 +1403,7 @@
         <v>108</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8314999999999999</v>
+        <v>1.0108</v>
       </c>
       <c r="N21" t="n">
         <v>155</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.93</v>
+        <v>1.0815</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1124</v>
+        <v>0.1307</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0457</v>
+        <v>-0.013</v>
       </c>
       <c r="E22" t="n">
-        <v>0.93</v>
+        <v>1.0815</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5174</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>0.4126</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5174</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4194</v>
+        <v>0.5422</v>
       </c>
       <c r="J22" t="n">
         <v>0.4126</v>
@@ -1449,7 +1449,7 @@
         <v>57</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8320000000000001</v>
+        <v>0.9548000000000001</v>
       </c>
       <c r="N22" t="n">
         <v>186</v>
@@ -1468,7 +1468,7 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.108</v>
+        <v>-0.1349</v>
       </c>
       <c r="E23" t="n">
         <v>0.7756999999999999</v>
@@ -1514,7 +1514,7 @@
         <v>0.0648</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2046</v>
+        <v>-0.2301</v>
       </c>
       <c r="E24" t="n">
         <v>0.5366</v>
@@ -1560,7 +1560,7 @@
         <v>0.0269</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3313</v>
+        <v>-0.3551</v>
       </c>
       <c r="E25" t="n">
         <v>0.2229</v>
@@ -1606,7 +1606,7 @@
         <v>0.0239</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3415</v>
+        <v>-0.3651</v>
       </c>
       <c r="E26" t="n">
         <v>0.1978</v>
@@ -1652,7 +1652,7 @@
         <v>-0.0012</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4253</v>
+        <v>-0.4478</v>
       </c>
       <c r="E27" t="n">
         <v>-0.0098</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0392</v>
+        <v>-0.0391</v>
       </c>
       <c r="C28" t="n">
         <v>-0.0047</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4372</v>
+        <v>-0.4595</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0392</v>
+        <v>-0.0391</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0392</v>
+        <v>-0.0391</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0392</v>
+        <v>-0.0391</v>
       </c>
       <c r="I28" t="n">
         <v>-0.0394</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0138</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4674</v>
+        <v>-0.4893</v>
       </c>
       <c r="E29" t="n">
         <v>-0.1139</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0519</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5948</v>
+        <v>-0.615</v>
       </c>
       <c r="E30" t="n">
         <v>-0.4294</v>
@@ -1836,7 +1836,7 @@
         <v>-0.0526</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5971</v>
+        <v>-0.6173</v>
       </c>
       <c r="E31" t="n">
         <v>-0.4351</v>
@@ -1882,7 +1882,7 @@
         <v>-0.0776</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.681</v>
+        <v>-0.6999</v>
       </c>
       <c r="E32" t="n">
         <v>-0.6425999999999999</v>
@@ -1928,7 +1928,7 @@
         <v>-0.078</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6823</v>
+        <v>-0.7012</v>
       </c>
       <c r="E33" t="n">
         <v>-0.6458</v>
@@ -1974,7 +1974,7 @@
         <v>-0.0813</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.7118</v>
       </c>
       <c r="E34" t="n">
         <v>-0.6725</v>
@@ -2020,7 +2020,7 @@
         <v>-0.1471</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9132</v>
+        <v>-0.929</v>
       </c>
       <c r="E35" t="n">
         <v>-1.2175</v>
@@ -2066,7 +2066,7 @@
         <v>-0.1557</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9421</v>
+        <v>-0.9575</v>
       </c>
       <c r="E36" t="n">
         <v>-1.2891</v>
@@ -2112,7 +2112,7 @@
         <v>-0.1625</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9646</v>
+        <v>-0.9796</v>
       </c>
       <c r="E37" t="n">
         <v>-1.3447</v>
@@ -2158,7 +2158,7 @@
         <v>-0.1963</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0776</v>
+        <v>-1.0911</v>
       </c>
       <c r="E38" t="n">
         <v>-1.6245</v>
@@ -2204,7 +2204,7 @@
         <v>-0.2179</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1501</v>
+        <v>-1.1626</v>
       </c>
       <c r="E39" t="n">
         <v>-1.8039</v>
@@ -2250,7 +2250,7 @@
         <v>-0.2808</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3602</v>
+        <v>-1.3698</v>
       </c>
       <c r="E40" t="n">
         <v>-2.324</v>
@@ -2296,7 +2296,7 @@
         <v>-0.3381</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5517</v>
+        <v>-1.5586</v>
       </c>
       <c r="E41" t="n">
         <v>-2.798</v>

--- a/database/event/2573/event_2573_evp_summary.xlsx
+++ b/database/event/2573/event_2573_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.9942</v>
+        <v>6.7601</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9659</v>
+        <v>0.8167</v>
       </c>
       <c r="D2" t="n">
-        <v>2.741</v>
+        <v>2.4138</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9942</v>
+        <v>6.7601</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2804</v>
+        <v>3.4136</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7138</v>
+        <v>3.3465</v>
       </c>
       <c r="H2" t="n">
-        <v>4.6604</v>
+        <v>6.5411</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7774</v>
+        <v>3.401</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7138</v>
+        <v>3.3465</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
@@ -529,7 +529,7 @@
         <v>147</v>
       </c>
       <c r="M2" t="n">
-        <v>7.4912</v>
+        <v>6.7475</v>
       </c>
       <c r="N2" t="n">
         <v>184</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.9194</v>
+        <v>5.6274</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7151999999999999</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9144</v>
+        <v>1.9025</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9194</v>
+        <v>5.6274</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2324</v>
+        <v>2.6569</v>
       </c>
       <c r="G3" t="n">
-        <v>3.687</v>
+        <v>2.9705</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2324</v>
+        <v>3.875</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8094</v>
+        <v>2.0148</v>
       </c>
       <c r="J3" t="n">
-        <v>3.687</v>
+        <v>2.9705</v>
       </c>
       <c r="K3" t="n">
         <v>37</v>
@@ -575,7 +575,7 @@
         <v>147</v>
       </c>
       <c r="M3" t="n">
-        <v>5.4964</v>
+        <v>4.985300000000001</v>
       </c>
       <c r="N3" t="n">
         <v>184</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5677</v>
+        <v>5.2428</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6727</v>
+        <v>0.6334</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7743</v>
+        <v>1.7288</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5677</v>
+        <v>5.2428</v>
       </c>
       <c r="F4" t="n">
-        <v>4.3977</v>
+        <v>4.0892</v>
       </c>
       <c r="G4" t="n">
-        <v>1.17</v>
+        <v>1.1536</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1325</v>
+        <v>8.9215</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1601</v>
+        <v>4.6388</v>
       </c>
       <c r="J4" t="n">
-        <v>1.17</v>
+        <v>1.1536</v>
       </c>
       <c r="K4" t="n">
         <v>84</v>
@@ -621,7 +621,7 @@
         <v>96</v>
       </c>
       <c r="M4" t="n">
-        <v>5.3301</v>
+        <v>5.7924</v>
       </c>
       <c r="N4" t="n">
         <v>180</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.2801</v>
+        <v>4.357</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6379</v>
+        <v>0.5264</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6597</v>
+        <v>1.329</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2801</v>
+        <v>4.357</v>
       </c>
       <c r="F5" t="n">
-        <v>3.8197</v>
+        <v>3.0506</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4604</v>
+        <v>1.3064</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8197</v>
+        <v>5.2623</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0959</v>
+        <v>2.7361</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4604</v>
+        <v>1.3064</v>
       </c>
       <c r="K5" t="n">
         <v>47</v>
@@ -667,7 +667,7 @@
         <v>108</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5563</v>
+        <v>4.0425</v>
       </c>
       <c r="N5" t="n">
         <v>155</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.6106</v>
+        <v>4.3253</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5226</v>
       </c>
       <c r="D6" t="n">
-        <v>1.393</v>
+        <v>1.3146</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6106</v>
+        <v>4.3253</v>
       </c>
       <c r="F6" t="n">
-        <v>4.3214</v>
+        <v>3.9232</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2892</v>
+        <v>0.4021</v>
       </c>
       <c r="H6" t="n">
-        <v>4.8256</v>
+        <v>8.336499999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>3.9113</v>
+        <v>4.3346</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2892</v>
+        <v>0.4021</v>
       </c>
       <c r="K6" t="n">
         <v>84</v>
@@ -713,7 +713,7 @@
         <v>96</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2005</v>
+        <v>4.7367</v>
       </c>
       <c r="N6" t="n">
         <v>180</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3623</v>
+        <v>4.0323</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4062</v>
+        <v>0.4872</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8956</v>
+        <v>1.1824</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3623</v>
+        <v>4.0323</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7206</v>
+        <v>1.5407</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6417</v>
+        <v>2.4916</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7206</v>
+        <v>1.5407</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5841</v>
+        <v>0.8011</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6417</v>
+        <v>2.4916</v>
       </c>
       <c r="K7" t="n">
         <v>37</v>
@@ -759,7 +759,7 @@
         <v>147</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2258</v>
+        <v>3.2927</v>
       </c>
       <c r="N7" t="n">
         <v>184</v>
@@ -768,35 +768,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0096</v>
+        <v>3.0548</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3636</v>
+        <v>0.3691</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7551</v>
+        <v>0.7411</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0096</v>
+        <v>3.0548</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3605</v>
+        <v>2.4061</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3509</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>3.3605</v>
+        <v>2.9912</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7238</v>
+        <v>1.5553</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3509</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="K8" t="n">
         <v>37</v>
@@ -805,7 +805,7 @@
         <v>147</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3729</v>
+        <v>2.204</v>
       </c>
       <c r="N8" t="n">
         <v>184</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9115</v>
+        <v>2.9416</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3518</v>
+        <v>0.3554</v>
       </c>
       <c r="D9" t="n">
-        <v>0.716</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9115</v>
+        <v>2.9416</v>
       </c>
       <c r="F9" t="n">
-        <v>3.3141</v>
+        <v>3.101</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4026</v>
+        <v>-0.1594</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3141</v>
+        <v>5.4396</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6862</v>
+        <v>2.8284</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4026</v>
+        <v>-0.1594</v>
       </c>
       <c r="K9" t="n">
         <v>84</v>
@@ -851,7 +851,7 @@
         <v>96</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2836</v>
+        <v>2.669</v>
       </c>
       <c r="N9" t="n">
         <v>180</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6344</v>
+        <v>2.8358</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3183</v>
+        <v>0.3426</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6056</v>
+        <v>0.6422</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6344</v>
+        <v>2.8358</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2814</v>
+        <v>3.1988</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.647</v>
+        <v>-0.363</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2814</v>
+        <v>5.7842</v>
       </c>
       <c r="I10" t="n">
-        <v>2.6597</v>
+        <v>3.0075</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.647</v>
+        <v>-0.363</v>
       </c>
       <c r="K10" t="n">
         <v>84</v>
@@ -897,7 +897,7 @@
         <v>96</v>
       </c>
       <c r="M10" t="n">
-        <v>2.0127</v>
+        <v>2.6445</v>
       </c>
       <c r="N10" t="n">
         <v>180</v>
@@ -906,47 +906,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6023</v>
+        <v>2.8209</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3144</v>
+        <v>0.3408</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5928</v>
+        <v>0.6355</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6023</v>
+        <v>2.8209</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8933</v>
+        <v>2.8209</v>
       </c>
       <c r="G11" t="n">
-        <v>0.709</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8933</v>
+        <v>2.8344</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5346</v>
+        <v>2.951</v>
       </c>
       <c r="J11" t="n">
-        <v>0.709</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>37</v>
+        <v>190</v>
       </c>
       <c r="L11" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.2436</v>
+        <v>2.951</v>
       </c>
       <c r="N11" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.3296</v>
+        <v>2.7174</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2815</v>
+        <v>0.3283</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4842</v>
+        <v>0.5888</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3296</v>
+        <v>2.7174</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3296</v>
+        <v>2.7174</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3296</v>
+        <v>2.7174</v>
       </c>
       <c r="I12" t="n">
-        <v>2.3492</v>
+        <v>2.8292</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3492</v>
+        <v>2.8292</v>
       </c>
       <c r="N12" t="n">
         <v>190</v>
@@ -998,47 +998,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.264</v>
+        <v>2.6707</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2735</v>
+        <v>0.3227</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4581</v>
+        <v>0.5677</v>
       </c>
       <c r="E13" t="n">
-        <v>2.264</v>
+        <v>2.6707</v>
       </c>
       <c r="F13" t="n">
-        <v>2.264</v>
+        <v>2.9472</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.2765</v>
       </c>
       <c r="H13" t="n">
-        <v>2.264</v>
+        <v>4.8979</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2831</v>
+        <v>2.5467</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.2765</v>
       </c>
       <c r="K13" t="n">
-        <v>190</v>
+        <v>37</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="M13" t="n">
-        <v>2.2831</v>
+        <v>2.2702</v>
       </c>
       <c r="N13" t="n">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1752</v>
+        <v>2.6383</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2628</v>
+        <v>0.3188</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4227</v>
+        <v>0.553</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1752</v>
+        <v>2.6383</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1197</v>
+        <v>2.4828</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0555</v>
+        <v>0.1555</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1197</v>
+        <v>3.2616</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7181</v>
+        <v>1.6959</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0555</v>
+        <v>0.1555</v>
       </c>
       <c r="K14" t="n">
         <v>129</v>
@@ -1081,7 +1081,7 @@
         <v>57</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7736</v>
+        <v>1.8514</v>
       </c>
       <c r="N14" t="n">
         <v>186</v>
@@ -1090,231 +1090,231 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8818</v>
+        <v>2.6242</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2274</v>
+        <v>0.3171</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3058</v>
+        <v>0.5467</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8818</v>
+        <v>2.6242</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3879</v>
+        <v>1.4596</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5061</v>
+        <v>1.1646</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3879</v>
+        <v>1.4596</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9355</v>
+        <v>0.7589</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5061</v>
+        <v>1.1646</v>
       </c>
       <c r="K15" t="n">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="L15" t="n">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4294</v>
+        <v>1.9235</v>
       </c>
       <c r="N15" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7441</v>
+        <v>2.5261</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2107</v>
+        <v>0.3052</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2509</v>
+        <v>0.5024</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7441</v>
+        <v>2.5261</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7441</v>
+        <v>2.2168</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.3093</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7441</v>
+        <v>2.3242</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7588</v>
+        <v>1.2085</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.3093</v>
       </c>
       <c r="K16" t="n">
-        <v>190</v>
+        <v>47</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7588</v>
+        <v>1.5178</v>
       </c>
       <c r="N16" t="n">
-        <v>190</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.7366</v>
+        <v>2.3697</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2098</v>
+        <v>0.2863</v>
       </c>
       <c r="D17" t="n">
-        <v>0.248</v>
+        <v>0.4318</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7366</v>
+        <v>2.3697</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7366</v>
+        <v>2.6715</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7366</v>
+        <v>3.9263</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7512</v>
+        <v>2.0415</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
       <c r="K17" t="n">
-        <v>190</v>
+        <v>129</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7512</v>
+        <v>1.7397</v>
       </c>
       <c r="N17" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>Nifty</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7281</v>
+        <v>2.2598</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2088</v>
+        <v>0.273</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2446</v>
+        <v>0.3822</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7281</v>
+        <v>2.2598</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3147</v>
+        <v>1.8098</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4134</v>
+        <v>0.45</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3147</v>
+        <v>1.8098</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0656</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4134</v>
+        <v>0.45</v>
       </c>
       <c r="K18" t="n">
-        <v>47</v>
+        <v>129</v>
       </c>
       <c r="L18" t="n">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="M18" t="n">
-        <v>1.479</v>
+        <v>1.391</v>
       </c>
       <c r="N18" t="n">
-        <v>155</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>keev</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.556</v>
+        <v>2.1495</v>
       </c>
       <c r="C19" t="n">
-        <v>0.188</v>
+        <v>0.2597</v>
       </c>
       <c r="D19" t="n">
-        <v>0.176</v>
+        <v>0.3324</v>
       </c>
       <c r="E19" t="n">
-        <v>1.556</v>
+        <v>2.1495</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3811</v>
+        <v>2.4828</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1749</v>
+        <v>-0.3333</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3811</v>
+        <v>3.2614</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3089</v>
+        <v>1.6958</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1749</v>
+        <v>-0.3333</v>
       </c>
       <c r="K19" t="n">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="L19" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4838</v>
+        <v>1.3625</v>
       </c>
       <c r="N19" t="n">
-        <v>180</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20">
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4098</v>
+        <v>2.1423</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1703</v>
+        <v>0.2588</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1178</v>
+        <v>0.3291</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4098</v>
+        <v>2.1423</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5034999999999999</v>
+        <v>1.1395</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9063</v>
+        <v>1.0028</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5034999999999999</v>
+        <v>1.1395</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4081</v>
+        <v>0.5925</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9063</v>
+        <v>1.0028</v>
       </c>
       <c r="K20" t="n">
         <v>47</v>
@@ -1357,7 +1357,7 @@
         <v>108</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3144</v>
+        <v>1.5953</v>
       </c>
       <c r="N20" t="n">
         <v>155</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>keev</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4073</v>
+        <v>2.0113</v>
       </c>
       <c r="C21" t="n">
-        <v>0.17</v>
+        <v>0.243</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1168</v>
+        <v>0.27</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4073</v>
+        <v>2.0113</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0925</v>
+        <v>2.0113</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6852</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0925</v>
+        <v>2.0113</v>
       </c>
       <c r="I21" t="n">
-        <v>1.696</v>
+        <v>2.094</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6852</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>47</v>
+        <v>190</v>
       </c>
       <c r="L21" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0108</v>
+        <v>2.094</v>
       </c>
       <c r="N21" t="n">
-        <v>155</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nifty</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0815</v>
+        <v>1.9364</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1307</v>
+        <v>0.234</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.013</v>
+        <v>0.2362</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0815</v>
+        <v>1.9364</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6689000000000001</v>
+        <v>1.9364</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4126</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6689000000000001</v>
+        <v>1.9364</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5422</v>
+        <v>2.016</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4126</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>129</v>
+        <v>190</v>
       </c>
       <c r="L22" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9548000000000001</v>
+        <v>2.016</v>
       </c>
       <c r="N22" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7756999999999999</v>
+        <v>1.1096</v>
       </c>
       <c r="C23" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1341</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1349</v>
+        <v>-0.1371</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7756999999999999</v>
+        <v>1.1096</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7756999999999999</v>
+        <v>1.1096</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7756999999999999</v>
+        <v>1.1096</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7756999999999999</v>
+        <v>1.1096</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7756999999999999</v>
+        <v>1.1096</v>
       </c>
       <c r="N23" t="n">
         <v>79</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5366</v>
+        <v>0.4527</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0648</v>
+        <v>0.0547</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2301</v>
+        <v>-0.4336</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5366</v>
+        <v>0.4527</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5366</v>
+        <v>0.4527</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5366</v>
+        <v>0.4527</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5366</v>
+        <v>0.4527</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5366</v>
+        <v>0.4527</v>
       </c>
       <c r="N24" t="n">
         <v>98</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2229</v>
+        <v>0.4358</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0269</v>
+        <v>0.0527</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3551</v>
+        <v>-0.4413</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2229</v>
+        <v>0.4358</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2229</v>
+        <v>0.4358</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2229</v>
+        <v>0.4358</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2229</v>
+        <v>0.4358</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2229</v>
+        <v>0.4358</v>
       </c>
       <c r="N25" t="n">
         <v>116</v>
@@ -1596,139 +1596,139 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>land1n</t>
+          <t>Ex6TenZ</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1978</v>
+        <v>0.4124</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0239</v>
+        <v>0.0498</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3651</v>
+        <v>-0.4518</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1978</v>
+        <v>0.4124</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1978</v>
+        <v>0.4124</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1978</v>
+        <v>0.4124</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1978</v>
+        <v>0.4124</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1978</v>
+        <v>0.4124</v>
       </c>
       <c r="N26" t="n">
-        <v>98</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ex6TenZ</t>
+          <t>FNS</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0098</v>
+        <v>0.3055</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0012</v>
+        <v>0.0369</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4478</v>
+        <v>-0.5001</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0098</v>
+        <v>0.3055</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0098</v>
+        <v>0.3055</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0098</v>
+        <v>0.3055</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0098</v>
+        <v>0.3181</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>116</v>
+        <v>190</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0098</v>
+        <v>0.3181</v>
       </c>
       <c r="N27" t="n">
-        <v>116</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FNS</t>
+          <t>land1n</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0391</v>
+        <v>0.2786</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0047</v>
+        <v>0.0337</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4595</v>
+        <v>-0.5122</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0391</v>
+        <v>0.2786</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0391</v>
+        <v>0.2786</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0391</v>
+        <v>0.2786</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0394</v>
+        <v>0.2786</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>190</v>
+        <v>98</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0394</v>
+        <v>0.2786</v>
       </c>
       <c r="N28" t="n">
-        <v>190</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1139</v>
+        <v>0.0324</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0138</v>
+        <v>0.0039</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4893</v>
+        <v>-0.6234</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1139</v>
+        <v>0.0324</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1139</v>
+        <v>0.0324</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1139</v>
+        <v>0.0324</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1139</v>
+        <v>0.0324</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1139</v>
+        <v>0.0324</v>
       </c>
       <c r="N29" t="n">
         <v>116</v>
@@ -1780,32 +1780,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AnJ</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4294</v>
+        <v>-0.1568</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0519</v>
+        <v>-0.0189</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.615</v>
+        <v>-0.7088</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4294</v>
+        <v>-0.1568</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.4294</v>
+        <v>-0.1568</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4294</v>
+        <v>-0.1568</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4294</v>
+        <v>-0.1568</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4294</v>
+        <v>-0.1568</v>
       </c>
       <c r="N30" t="n">
         <v>79</v>
@@ -1826,32 +1826,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>AnJ</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4351</v>
+        <v>-0.2026</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0526</v>
+        <v>-0.0245</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6173</v>
+        <v>-0.7295</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4351</v>
+        <v>-0.2026</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4351</v>
+        <v>-0.2026</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4351</v>
+        <v>-0.2026</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4351</v>
+        <v>-0.2026</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4351</v>
+        <v>-0.2026</v>
       </c>
       <c r="N31" t="n">
         <v>79</v>
@@ -1872,170 +1872,170 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ALEX</t>
+          <t>RIKO</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.2382</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0776</v>
+        <v>-0.0288</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6999</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.2382</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.2382</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.2382</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.2382</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.2382</v>
       </c>
       <c r="N32" t="n">
-        <v>116</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LEGIJA</t>
+          <t>ALEX</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6458</v>
+        <v>-0.3976</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.078</v>
+        <v>-0.048</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7012</v>
+        <v>-0.8175</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6458</v>
+        <v>-0.3976</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.351</v>
+        <v>-0.3976</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.2948</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.351</v>
+        <v>-0.3976</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2845</v>
+        <v>-0.3976</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.2948</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c r="L33" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5792999999999999</v>
+        <v>-0.3976</v>
       </c>
       <c r="N33" t="n">
-        <v>155</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RIKO</t>
+          <t>LEGIJA</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6725</v>
+        <v>-0.5305</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0813</v>
+        <v>-0.0641</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7118</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6725</v>
+        <v>-0.5305</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6725</v>
+        <v>-0.2504</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.2801</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6725</v>
+        <v>-0.2504</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6725</v>
+        <v>-0.1302</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.2801</v>
       </c>
       <c r="K34" t="n">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6725</v>
+        <v>-0.4103</v>
       </c>
       <c r="N34" t="n">
-        <v>79</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tatazin</t>
+          <t>dzt</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.2175</v>
+        <v>-0.7608</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1471</v>
+        <v>-0.0919</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.929</v>
+        <v>-0.9815</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.2175</v>
+        <v>-0.7608</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.2175</v>
+        <v>-0.7608</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.2175</v>
+        <v>-0.7608</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.2175</v>
+        <v>-0.7608</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.2175</v>
+        <v>-0.7608</v>
       </c>
       <c r="N35" t="n">
         <v>98</v>
@@ -2056,32 +2056,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>dzt</t>
+          <t>tatazin</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2891</v>
+        <v>-0.8955</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1557</v>
+        <v>-0.1082</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9575</v>
+        <v>-1.0423</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2891</v>
+        <v>-0.8955</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.2891</v>
+        <v>-0.8955</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.2891</v>
+        <v>-0.8955</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.2891</v>
+        <v>-0.8955</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.2891</v>
+        <v>-0.8955</v>
       </c>
       <c r="N36" t="n">
         <v>98</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3447</v>
+        <v>-1.1242</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1625</v>
+        <v>-0.1358</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9796</v>
+        <v>-1.1455</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3447</v>
+        <v>-1.1242</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.3335</v>
+        <v>-1.1242</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.0112</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.3335</v>
+        <v>-1.1242</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.0808</v>
+        <v>-1.1242</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.0112</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="L37" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.092</v>
+        <v>-1.1242</v>
       </c>
       <c r="N37" t="n">
-        <v>186</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.6245</v>
+        <v>-1.311</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1963</v>
+        <v>-0.1584</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0911</v>
+        <v>-1.2299</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.6245</v>
+        <v>-1.311</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.6245</v>
+        <v>-1.4403</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.1293</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.6245</v>
+        <v>-1.4403</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.6245</v>
+        <v>-0.7489</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>0.1293</v>
       </c>
       <c r="K38" t="n">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.6245</v>
+        <v>-0.6196</v>
       </c>
       <c r="N38" t="n">
-        <v>79</v>
+        <v>186</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.8039</v>
+        <v>-1.4144</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2179</v>
+        <v>-0.1709</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1626</v>
+        <v>-1.2765</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.8039</v>
+        <v>-1.4144</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.8039</v>
+        <v>-1.4144</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.8039</v>
+        <v>-1.4144</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.8039</v>
+        <v>-1.4144</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.8039</v>
+        <v>-1.4144</v>
       </c>
       <c r="N39" t="n">
         <v>98</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.324</v>
+        <v>-1.9605</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2808</v>
+        <v>-0.2369</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3698</v>
+        <v>-1.5231</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.324</v>
+        <v>-1.9605</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.324</v>
+        <v>-1.9605</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.324</v>
+        <v>-1.9605</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.324</v>
+        <v>-1.9605</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.324</v>
+        <v>-1.9605</v>
       </c>
       <c r="N40" t="n">
         <v>116</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.798</v>
+        <v>-3.0771</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3381</v>
+        <v>-0.3718</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5586</v>
+        <v>-2.0272</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.798</v>
+        <v>-3.0771</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.7313</v>
+        <v>-3.1878</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.0667</v>
+        <v>0.1107</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.7313</v>
+        <v>-3.1878</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.2138</v>
+        <v>-1.6575</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.0667</v>
+        <v>0.1107</v>
       </c>
       <c r="K41" t="n">
         <v>129</v>
@@ -2323,7 +2323,7 @@
         <v>57</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.2805</v>
+        <v>-1.5468</v>
       </c>
       <c r="N41" t="n">
         <v>186</v>
@@ -2429,10 +2429,10 @@
         <v>1.28</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5084</v>
+        <v>0.5988</v>
       </c>
       <c r="J2" t="n">
-        <v>14.7436</v>
+        <v>17.3652</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.19</v>
       </c>
       <c r="I3" t="n">
-        <v>0.384</v>
+        <v>0.4345</v>
       </c>
       <c r="J3" t="n">
-        <v>11.136</v>
+        <v>12.6005</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.11</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2606</v>
+        <v>0.2784</v>
       </c>
       <c r="J4" t="n">
-        <v>7.5574</v>
+        <v>8.073600000000001</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.61</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6271</v>
+        <v>-0.4155</v>
       </c>
       <c r="J5" t="n">
-        <v>-18.1859</v>
+        <v>-12.0495</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.6</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6395</v>
+        <v>-0.4247</v>
       </c>
       <c r="J6" t="n">
-        <v>-18.5455</v>
+        <v>-12.3163</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.62</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4542</v>
+        <v>1.2925</v>
       </c>
       <c r="J7" t="n">
-        <v>42.1718</v>
+        <v>37.4825</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.3</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7907</v>
+        <v>0.793</v>
       </c>
       <c r="J8" t="n">
-        <v>22.9303</v>
+        <v>22.997</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4046</v>
+        <v>0.4622</v>
       </c>
       <c r="J9" t="n">
-        <v>11.7334</v>
+        <v>13.4038</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.02</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0235</v>
+        <v>0.0469</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6815</v>
+        <v>1.3601</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.91</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4489</v>
+        <v>-0.3747</v>
       </c>
       <c r="J11" t="n">
-        <v>-13.0181</v>
+        <v>-10.8663</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.89</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0925</v>
+        <v>-0.1004</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.035</v>
+        <v>-2.2088</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.83</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.192</v>
+        <v>-0.1686</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.224</v>
+        <v>-3.7092</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.77</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2888</v>
+        <v>-0.2313</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.3536</v>
+        <v>-5.0886</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.62</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5481</v>
+        <v>-0.3709</v>
       </c>
       <c r="J15" t="n">
-        <v>-12.0582</v>
+        <v>-8.159800000000001</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.4</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.838</v>
+        <v>-0.5764</v>
       </c>
       <c r="J16" t="n">
-        <v>-18.436</v>
+        <v>-12.6808</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.69</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4739</v>
+        <v>1.3218</v>
       </c>
       <c r="J17" t="n">
-        <v>32.4258</v>
+        <v>29.0796</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.5</v>
       </c>
       <c r="I18" t="n">
-        <v>1.098</v>
+        <v>1.0982</v>
       </c>
       <c r="J18" t="n">
-        <v>24.156</v>
+        <v>24.1604</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.46</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0064</v>
+        <v>1.0504</v>
       </c>
       <c r="J19" t="n">
-        <v>22.1408</v>
+        <v>23.1088</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.45</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9797</v>
+        <v>1.0378</v>
       </c>
       <c r="J20" t="n">
-        <v>21.5534</v>
+        <v>22.8316</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.14</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2548</v>
+        <v>0.3562</v>
       </c>
       <c r="J21" t="n">
-        <v>5.6056</v>
+        <v>7.8364</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.5</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2669</v>
+        <v>0.892</v>
       </c>
       <c r="J22" t="n">
-        <v>38.007</v>
+        <v>26.76</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.15</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4628</v>
+        <v>0.4039</v>
       </c>
       <c r="J23" t="n">
-        <v>13.884</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.15</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4628</v>
+        <v>0.4039</v>
       </c>
       <c r="J24" t="n">
-        <v>13.884</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.96</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.262</v>
+        <v>-0.1941</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.86</v>
+        <v>-5.823</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.8</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7062</v>
+        <v>-0.653</v>
       </c>
       <c r="J26" t="n">
-        <v>-21.186</v>
+        <v>-19.59</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.21</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3917</v>
+        <v>0.4031</v>
       </c>
       <c r="J27" t="n">
-        <v>11.751</v>
+        <v>12.093</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.19</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3628</v>
+        <v>0.3816</v>
       </c>
       <c r="J28" t="n">
-        <v>10.884</v>
+        <v>11.448</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.11</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2379</v>
+        <v>0.2622</v>
       </c>
       <c r="J29" t="n">
-        <v>7.137</v>
+        <v>7.866</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.84</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3289</v>
+        <v>-0.2004</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.867000000000001</v>
+        <v>-6.012</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.74</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4707</v>
+        <v>-0.3</v>
       </c>
       <c r="J31" t="n">
-        <v>-14.121</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.2</v>
       </c>
       <c r="I32" t="n">
-        <v>0.427</v>
+        <v>0.3564</v>
       </c>
       <c r="J32" t="n">
-        <v>11.102</v>
+        <v>9.266400000000001</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0613</v>
+        <v>0.0205</v>
       </c>
       <c r="J33" t="n">
-        <v>1.5938</v>
+        <v>0.533</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.91</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1424</v>
+        <v>-0.1117</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.7024</v>
+        <v>-2.9042</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.67</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.35</v>
       </c>
       <c r="J35" t="n">
-        <v>-13.9048</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.62</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6002</v>
+        <v>-0.3969</v>
       </c>
       <c r="J36" t="n">
-        <v>-15.6052</v>
+        <v>-10.3194</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.37</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5353</v>
+        <v>0.4162</v>
       </c>
       <c r="J37" t="n">
-        <v>13.9178</v>
+        <v>10.8212</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.24</v>
       </c>
       <c r="I38" t="n">
-        <v>0.352</v>
+        <v>0.3239</v>
       </c>
       <c r="J38" t="n">
-        <v>9.151999999999999</v>
+        <v>8.4214</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.22</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3143</v>
+        <v>0.3027</v>
       </c>
       <c r="J39" t="n">
-        <v>8.171799999999999</v>
+        <v>7.8702</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.21</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2983</v>
+        <v>0.291</v>
       </c>
       <c r="J40" t="n">
-        <v>7.7558</v>
+        <v>7.566</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.14</v>
       </c>
       <c r="I41" t="n">
-        <v>0.19</v>
+        <v>0.2028</v>
       </c>
       <c r="J41" t="n">
-        <v>4.94</v>
+        <v>5.2728</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.46</v>
       </c>
       <c r="I42" t="n">
-        <v>1.1522</v>
+        <v>0.8215</v>
       </c>
       <c r="J42" t="n">
-        <v>46.088</v>
+        <v>32.86</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.4</v>
       </c>
       <c r="I43" t="n">
-        <v>1.0269</v>
+        <v>0.7428</v>
       </c>
       <c r="J43" t="n">
-        <v>41.076</v>
+        <v>29.712</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.27</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7333</v>
+        <v>0.5672</v>
       </c>
       <c r="J44" t="n">
-        <v>29.332</v>
+        <v>22.688</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1149</v>
+        <v>-0.043</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.596</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.76</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8175</v>
+        <v>-0.7716</v>
       </c>
       <c r="J46" t="n">
-        <v>-32.7</v>
+        <v>-30.864</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.25</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4689</v>
+        <v>0.4588</v>
       </c>
       <c r="J47" t="n">
-        <v>18.756</v>
+        <v>18.352</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.24</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4552</v>
+        <v>0.4481</v>
       </c>
       <c r="J48" t="n">
-        <v>18.208</v>
+        <v>17.924</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.88</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.247</v>
+        <v>-0.1511</v>
       </c>
       <c r="J49" t="n">
-        <v>-9.880000000000001</v>
+        <v>-6.044</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.87</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2637</v>
+        <v>-0.1618</v>
       </c>
       <c r="J50" t="n">
-        <v>-10.548</v>
+        <v>-6.472</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.54</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.7116</v>
+        <v>-0.4792</v>
       </c>
       <c r="J51" t="n">
-        <v>-28.464</v>
+        <v>-19.168</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.36</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.6819</v>
       </c>
       <c r="J52" t="n">
-        <v>24.8103</v>
+        <v>18.4113</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.29</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7573</v>
+        <v>0.5884</v>
       </c>
       <c r="J53" t="n">
-        <v>20.4471</v>
+        <v>15.8868</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.2</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5053</v>
+        <v>0.4659</v>
       </c>
       <c r="J54" t="n">
-        <v>13.6431</v>
+        <v>12.5793</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.13</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3122</v>
+        <v>0.3615</v>
       </c>
       <c r="J55" t="n">
-        <v>8.429399999999999</v>
+        <v>9.7605</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.11</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2562</v>
+        <v>0.3243</v>
       </c>
       <c r="J56" t="n">
-        <v>6.9174</v>
+        <v>8.7561</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.12</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2822</v>
+        <v>0.3031</v>
       </c>
       <c r="J57" t="n">
-        <v>7.6194</v>
+        <v>8.1837</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.1</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2492</v>
+        <v>0.2622</v>
       </c>
       <c r="J58" t="n">
-        <v>6.7284</v>
+        <v>7.0794</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.91</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1886</v>
+        <v>-0.1171</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.0922</v>
+        <v>-3.1617</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.8</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3693</v>
+        <v>-0.2323</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.9711</v>
+        <v>-6.2721</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.79</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.384</v>
+        <v>-0.2423</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.368</v>
+        <v>-6.5421</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.21</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6636</v>
+        <v>0.5064</v>
       </c>
       <c r="J62" t="n">
-        <v>19.908</v>
+        <v>15.192</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.11</v>
       </c>
       <c r="I63" t="n">
-        <v>0.393</v>
+        <v>0.3503</v>
       </c>
       <c r="J63" t="n">
-        <v>11.79</v>
+        <v>10.509</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.05</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1887</v>
+        <v>0.1865</v>
       </c>
       <c r="J64" t="n">
-        <v>5.661</v>
+        <v>5.595</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.99</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1099</v>
+        <v>-0.0643</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.297</v>
+        <v>-1.929</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.88</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4773</v>
+        <v>-0.4197</v>
       </c>
       <c r="J66" t="n">
-        <v>-14.319</v>
+        <v>-12.591</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.38</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6012</v>
+        <v>0.5671</v>
       </c>
       <c r="J67" t="n">
-        <v>18.036</v>
+        <v>17.013</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.17</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3173</v>
+        <v>0.353</v>
       </c>
       <c r="J68" t="n">
-        <v>9.519</v>
+        <v>10.59</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.96</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1368</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.104</v>
+        <v>-2.085</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.93</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1937</v>
+        <v>-0.1067</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.811</v>
+        <v>-3.201</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.87</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2934</v>
+        <v>-0.1738</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.802</v>
+        <v>-5.214</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.83</v>
       </c>
       <c r="I72" t="n">
-        <v>1.6512</v>
+        <v>1.4515</v>
       </c>
       <c r="J72" t="n">
-        <v>29.7216</v>
+        <v>26.127</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.73</v>
       </c>
       <c r="I73" t="n">
-        <v>1.4676</v>
+        <v>1.3414</v>
       </c>
       <c r="J73" t="n">
-        <v>26.4168</v>
+        <v>24.1452</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.71</v>
       </c>
       <c r="I74" t="n">
-        <v>1.4292</v>
+        <v>1.3193</v>
       </c>
       <c r="J74" t="n">
-        <v>25.7256</v>
+        <v>23.7474</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.57</v>
       </c>
       <c r="I75" t="n">
-        <v>1.1243</v>
+        <v>1.1642</v>
       </c>
       <c r="J75" t="n">
-        <v>20.2374</v>
+        <v>20.9556</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.33</v>
       </c>
       <c r="I76" t="n">
-        <v>0.6374</v>
+        <v>0.778</v>
       </c>
       <c r="J76" t="n">
-        <v>11.4732</v>
+        <v>14.004</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.42</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.6332</v>
+        <v>-0.4929</v>
       </c>
       <c r="J77" t="n">
-        <v>-11.3976</v>
+        <v>-8.872199999999999</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.4</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.6717</v>
+        <v>-0.5124</v>
       </c>
       <c r="J78" t="n">
-        <v>-12.0906</v>
+        <v>-9.2232</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.37</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.748</v>
+        <v>-0.539</v>
       </c>
       <c r="J79" t="n">
-        <v>-13.464</v>
+        <v>-9.702</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.37</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.748</v>
+        <v>-0.539</v>
       </c>
       <c r="J80" t="n">
-        <v>-13.464</v>
+        <v>-9.702</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.36</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7679</v>
+        <v>-0.5484</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.8222</v>
+        <v>-9.8712</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>2.2</v>
       </c>
       <c r="I82" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J82" t="n">
-        <v>41.186</v>
+        <v>36.676</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.47</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9805</v>
+        <v>1.0589</v>
       </c>
       <c r="J83" t="n">
-        <v>19.61</v>
+        <v>21.178</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.3</v>
       </c>
       <c r="I84" t="n">
-        <v>0.6113</v>
+        <v>0.7357</v>
       </c>
       <c r="J84" t="n">
-        <v>12.226</v>
+        <v>14.714</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.3</v>
       </c>
       <c r="I85" t="n">
-        <v>0.6113</v>
+        <v>0.7357</v>
       </c>
       <c r="J85" t="n">
-        <v>12.226</v>
+        <v>14.714</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.24</v>
       </c>
       <c r="I86" t="n">
-        <v>0.4777</v>
+        <v>0.596</v>
       </c>
       <c r="J86" t="n">
-        <v>9.554</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.88</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.1076</v>
+        <v>-0.1111</v>
       </c>
       <c r="J87" t="n">
-        <v>-2.152</v>
+        <v>-2.222</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.78</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2704</v>
+        <v>-0.2204</v>
       </c>
       <c r="J88" t="n">
-        <v>-5.408</v>
+        <v>-4.408</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.73</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3524</v>
+        <v>-0.2698</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.048</v>
+        <v>-5.396</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.68</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4513</v>
+        <v>-0.3149</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.026</v>
+        <v>-6.298</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.42</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.8127</v>
+        <v>-0.5572</v>
       </c>
       <c r="J91" t="n">
-        <v>-16.254</v>
+        <v>-11.144</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.47</v>
       </c>
       <c r="I92" t="n">
-        <v>1.2024</v>
+        <v>1.1238</v>
       </c>
       <c r="J92" t="n">
-        <v>34.8696</v>
+        <v>32.5902</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.16</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4854</v>
+        <v>0.4764</v>
       </c>
       <c r="J93" t="n">
-        <v>14.0766</v>
+        <v>13.8156</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.08</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2219</v>
+        <v>0.2634</v>
       </c>
       <c r="J94" t="n">
-        <v>6.4351</v>
+        <v>7.6386</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.95</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.299</v>
+        <v>-0.2296</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.670999999999999</v>
+        <v>-6.6584</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3311</v>
+        <v>-0.2618</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.601900000000001</v>
+        <v>-7.5922</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.22</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4059</v>
+        <v>0.4694</v>
       </c>
       <c r="J97" t="n">
-        <v>11.7711</v>
+        <v>13.6126</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.21</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3917</v>
+        <v>0.4513</v>
       </c>
       <c r="J98" t="n">
-        <v>11.3593</v>
+        <v>13.0877</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.08</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1853</v>
+        <v>0.201</v>
       </c>
       <c r="J99" t="n">
-        <v>5.3737</v>
+        <v>5.829</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.8</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3877</v>
+        <v>-0.2411</v>
       </c>
       <c r="J100" t="n">
-        <v>-11.2433</v>
+        <v>-6.9919</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.78</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.416</v>
+        <v>-0.261</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.064</v>
+        <v>-7.569</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.26</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4699</v>
+        <v>0.4207</v>
       </c>
       <c r="J102" t="n">
-        <v>12.2174</v>
+        <v>10.9382</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.17</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3424</v>
+        <v>0.2949</v>
       </c>
       <c r="J103" t="n">
-        <v>8.9024</v>
+        <v>7.6674</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.91</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2078</v>
+        <v>-0.1222</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.4028</v>
+        <v>-3.1772</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.85</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3069</v>
+        <v>-0.187</v>
       </c>
       <c r="J105" t="n">
-        <v>-7.9794</v>
+        <v>-4.862</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.77</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4243</v>
+        <v>-0.2678</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.0318</v>
+        <v>-6.9628</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.29</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4509</v>
+        <v>0.3915</v>
       </c>
       <c r="J107" t="n">
-        <v>11.7234</v>
+        <v>10.179</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.23</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3663</v>
+        <v>0.3202</v>
       </c>
       <c r="J108" t="n">
-        <v>9.5238</v>
+        <v>8.325200000000001</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.15</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2286</v>
+        <v>0.2226</v>
       </c>
       <c r="J109" t="n">
-        <v>5.9436</v>
+        <v>5.7876</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.12</v>
       </c>
       <c r="I110" t="n">
-        <v>0.178</v>
+        <v>0.1831</v>
       </c>
       <c r="J110" t="n">
-        <v>4.628</v>
+        <v>4.7606</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.07</v>
       </c>
       <c r="I111" t="n">
-        <v>0.0919</v>
+        <v>0.1115</v>
       </c>
       <c r="J111" t="n">
-        <v>2.3894</v>
+        <v>2.899</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.46</v>
       </c>
       <c r="I112" t="n">
-        <v>1.1799</v>
+        <v>1.1095</v>
       </c>
       <c r="J112" t="n">
-        <v>31.8573</v>
+        <v>29.9565</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.06</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1541</v>
+        <v>0.2025</v>
       </c>
       <c r="J113" t="n">
-        <v>4.1607</v>
+        <v>5.4675</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.05</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1205</v>
+        <v>0.171</v>
       </c>
       <c r="J114" t="n">
-        <v>3.2535</v>
+        <v>4.617</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.03</v>
       </c>
       <c r="I115" t="n">
-        <v>0.0495</v>
+        <v>0.1035</v>
       </c>
       <c r="J115" t="n">
-        <v>1.3365</v>
+        <v>2.7945</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.02</v>
       </c>
       <c r="I116" t="n">
-        <v>0.0108</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="J116" t="n">
-        <v>0.2916</v>
+        <v>1.7982</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.33</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5431</v>
+        <v>0.6511</v>
       </c>
       <c r="J117" t="n">
-        <v>14.6637</v>
+        <v>17.5797</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.07</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1523</v>
+        <v>0.1745</v>
       </c>
       <c r="J118" t="n">
-        <v>4.1121</v>
+        <v>4.7115</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.06</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1316</v>
+        <v>0.1533</v>
       </c>
       <c r="J119" t="n">
-        <v>3.5532</v>
+        <v>4.1391</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.06</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1316</v>
+        <v>0.1533</v>
       </c>
       <c r="J120" t="n">
-        <v>3.5532</v>
+        <v>4.1391</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.72</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5026</v>
+        <v>-0.3225</v>
       </c>
       <c r="J121" t="n">
-        <v>-13.5702</v>
+        <v>-8.7075</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.22</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.6208</v>
       </c>
       <c r="J122" t="n">
-        <v>18.978</v>
+        <v>18.624</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.19</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.5471</v>
       </c>
       <c r="J123" t="n">
-        <v>16.617</v>
+        <v>16.413</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.18</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5265</v>
+        <v>0.5223</v>
       </c>
       <c r="J124" t="n">
-        <v>15.795</v>
+        <v>15.669</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.18</v>
       </c>
       <c r="I125" t="n">
-        <v>0.5265</v>
+        <v>0.5223</v>
       </c>
       <c r="J125" t="n">
-        <v>15.795</v>
+        <v>15.669</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.93</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3698</v>
+        <v>-0.2984</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.094</v>
+        <v>-8.952</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.21</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4227</v>
+        <v>0.4828</v>
       </c>
       <c r="J127" t="n">
-        <v>12.681</v>
+        <v>14.484</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.16</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3497</v>
+        <v>0.3874</v>
       </c>
       <c r="J128" t="n">
-        <v>10.491</v>
+        <v>11.622</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.8</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3653</v>
+        <v>-0.2306</v>
       </c>
       <c r="J129" t="n">
-        <v>-10.959</v>
+        <v>-6.918</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.79</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3801</v>
+        <v>-0.2406</v>
       </c>
       <c r="J130" t="n">
-        <v>-11.403</v>
+        <v>-7.218</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5196</v>
+        <v>-0.3375</v>
       </c>
       <c r="J131" t="n">
-        <v>-15.588</v>
+        <v>-10.125</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.42</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0775</v>
+        <v>1.0459</v>
       </c>
       <c r="J132" t="n">
-        <v>30.17</v>
+        <v>29.2852</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.29</v>
       </c>
       <c r="I133" t="n">
-        <v>0.7903</v>
+        <v>0.7815</v>
       </c>
       <c r="J133" t="n">
-        <v>22.1284</v>
+        <v>21.882</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.28</v>
       </c>
       <c r="I134" t="n">
-        <v>0.7667</v>
+        <v>0.758</v>
       </c>
       <c r="J134" t="n">
-        <v>21.4676</v>
+        <v>21.224</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.04</v>
       </c>
       <c r="I135" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.1287</v>
       </c>
       <c r="J135" t="n">
-        <v>1.8648</v>
+        <v>3.6036</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.78</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7675</v>
+        <v>-0.7171999999999999</v>
       </c>
       <c r="J136" t="n">
-        <v>-21.49</v>
+        <v>-20.0816</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.5</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.9716</v>
       </c>
       <c r="J137" t="n">
-        <v>21.8316</v>
+        <v>27.2048</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.1</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2455</v>
+        <v>0.2591</v>
       </c>
       <c r="J138" t="n">
-        <v>6.874</v>
+        <v>7.2548</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.82</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.3422</v>
+        <v>-0.2134</v>
       </c>
       <c r="J139" t="n">
-        <v>-9.5816</v>
+        <v>-5.9752</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.5246</v>
+        <v>-0.3404</v>
       </c>
       <c r="J140" t="n">
-        <v>-14.6888</v>
+        <v>-9.5312</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.66</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5635</v>
+        <v>-0.3686</v>
       </c>
       <c r="J141" t="n">
-        <v>-15.778</v>
+        <v>-10.3208</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.1</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2576</v>
+        <v>0.2694</v>
       </c>
       <c r="J142" t="n">
-        <v>7.4704</v>
+        <v>7.8126</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.99</v>
       </c>
       <c r="I143" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0132</v>
       </c>
       <c r="J143" t="n">
-        <v>0.2436</v>
+        <v>-0.3828</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.91</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1764</v>
+        <v>-0.1151</v>
       </c>
       <c r="J144" t="n">
-        <v>-5.1156</v>
+        <v>-3.3379</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.89</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2152</v>
+        <v>-0.1368</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.2408</v>
+        <v>-3.9672</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.72</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4773</v>
+        <v>-0.3079</v>
       </c>
       <c r="J146" t="n">
-        <v>-13.8417</v>
+        <v>-8.9291</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.33</v>
       </c>
       <c r="I147" t="n">
-        <v>0.8778</v>
+        <v>0.8718</v>
       </c>
       <c r="J147" t="n">
-        <v>25.4562</v>
+        <v>25.2822</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.24</v>
       </c>
       <c r="I148" t="n">
-        <v>0.6642</v>
+        <v>0.6611</v>
       </c>
       <c r="J148" t="n">
-        <v>19.2618</v>
+        <v>19.1719</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.19</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.5407</v>
       </c>
       <c r="J149" t="n">
-        <v>15.3903</v>
+        <v>15.6803</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.05</v>
       </c>
       <c r="I150" t="n">
-        <v>0.0968</v>
+        <v>0.1597</v>
       </c>
       <c r="J150" t="n">
-        <v>2.8072</v>
+        <v>4.6313</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.04</v>
       </c>
       <c r="I151" t="n">
-        <v>0.0629</v>
+        <v>0.1267</v>
       </c>
       <c r="J151" t="n">
-        <v>1.8241</v>
+        <v>3.6743</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.46</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6812</v>
+        <v>0.5988</v>
       </c>
       <c r="J152" t="n">
-        <v>19.7548</v>
+        <v>17.3652</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.17</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2975</v>
+        <v>0.2531</v>
       </c>
       <c r="J153" t="n">
-        <v>8.6275</v>
+        <v>7.3399</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.13</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2304</v>
+        <v>0.2013</v>
       </c>
       <c r="J154" t="n">
-        <v>6.6816</v>
+        <v>5.8377</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.92</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2241</v>
+        <v>-0.1239</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.4989</v>
+        <v>-3.5931</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.89</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2734</v>
+        <v>-0.1577</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.9286</v>
+        <v>-4.5733</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.08</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1935</v>
+        <v>0.1572</v>
       </c>
       <c r="J157" t="n">
-        <v>5.6115</v>
+        <v>4.5588</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.08</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1935</v>
+        <v>0.1572</v>
       </c>
       <c r="J158" t="n">
-        <v>5.6115</v>
+        <v>4.5588</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.03</v>
       </c>
       <c r="I159" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="J159" t="n">
-        <v>2.7057</v>
+        <v>2.0445</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.99</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.0391</v>
+        <v>-0.0204</v>
       </c>
       <c r="J160" t="n">
-        <v>-1.1339</v>
+        <v>-0.5916</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3686</v>
+        <v>-0.2287</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.6894</v>
+        <v>-6.6323</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.08</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3295</v>
+        <v>0.3603</v>
       </c>
       <c r="J162" t="n">
-        <v>6.59</v>
+        <v>7.206</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>0.0707</v>
+        <v>0.0266</v>
       </c>
       <c r="J163" t="n">
-        <v>1.414</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.55</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.6369</v>
+        <v>-0.4316</v>
       </c>
       <c r="J164" t="n">
-        <v>-12.738</v>
+        <v>-8.632</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.44</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.7824</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="J165" t="n">
-        <v>-15.648</v>
+        <v>-10.696</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.33</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.9174</v>
+        <v>-0.638</v>
       </c>
       <c r="J166" t="n">
-        <v>-18.348</v>
+        <v>-12.76</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.68</v>
       </c>
       <c r="I167" t="n">
-        <v>1.4725</v>
+        <v>1.3174</v>
       </c>
       <c r="J167" t="n">
-        <v>29.45</v>
+        <v>26.348</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.57</v>
       </c>
       <c r="I168" t="n">
-        <v>1.2623</v>
+        <v>1.1871</v>
       </c>
       <c r="J168" t="n">
-        <v>25.246</v>
+        <v>23.742</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.47</v>
       </c>
       <c r="I169" t="n">
-        <v>1.0559</v>
+        <v>1.0668</v>
       </c>
       <c r="J169" t="n">
-        <v>21.118</v>
+        <v>21.336</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.37</v>
       </c>
       <c r="I170" t="n">
-        <v>0.8076</v>
+        <v>0.9076</v>
       </c>
       <c r="J170" t="n">
-        <v>16.152</v>
+        <v>18.152</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.95</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3832</v>
+        <v>-0.2978</v>
       </c>
       <c r="J171" t="n">
-        <v>-7.664</v>
+        <v>-5.956</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.45</v>
       </c>
       <c r="I172" t="n">
-        <v>0.7138</v>
+        <v>0.8828</v>
       </c>
       <c r="J172" t="n">
-        <v>18.5588</v>
+        <v>22.9528</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.07</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1841</v>
+        <v>0.1893</v>
       </c>
       <c r="J173" t="n">
-        <v>4.7866</v>
+        <v>4.9218</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.97</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0481</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.0332</v>
+        <v>-1.2506</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2539</v>
+        <v>-0.1534</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.6014</v>
+        <v>-3.9884</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.51</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.7494</v>
+        <v>-0.5082</v>
       </c>
       <c r="J176" t="n">
-        <v>-19.4844</v>
+        <v>-13.2132</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.74</v>
       </c>
       <c r="I177" t="n">
-        <v>1.7019</v>
+        <v>1.4599</v>
       </c>
       <c r="J177" t="n">
-        <v>44.2494</v>
+        <v>37.9574</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.22</v>
       </c>
       <c r="I178" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.6187</v>
       </c>
       <c r="J178" t="n">
-        <v>16.315</v>
+        <v>16.0862</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.07</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1726</v>
+        <v>0.2274</v>
       </c>
       <c r="J179" t="n">
-        <v>4.4876</v>
+        <v>5.9124</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.96</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2768</v>
+        <v>-0.2036</v>
       </c>
       <c r="J180" t="n">
-        <v>-7.1968</v>
+        <v>-5.2936</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.75</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.8331</v>
+        <v>-0.7894</v>
       </c>
       <c r="J181" t="n">
-        <v>-21.6606</v>
+        <v>-20.5244</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>2.32</v>
       </c>
       <c r="I182" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J182" t="n">
-        <v>35.0081</v>
+        <v>31.1746</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.72</v>
       </c>
       <c r="I183" t="n">
-        <v>1.4347</v>
+        <v>1.3276</v>
       </c>
       <c r="J183" t="n">
-        <v>24.3899</v>
+        <v>22.5692</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.69</v>
       </c>
       <c r="I184" t="n">
-        <v>1.374</v>
+        <v>1.2948</v>
       </c>
       <c r="J184" t="n">
-        <v>23.358</v>
+        <v>22.0116</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.54</v>
       </c>
       <c r="I185" t="n">
-        <v>1.0524</v>
+        <v>1.1268</v>
       </c>
       <c r="J185" t="n">
-        <v>17.8908</v>
+        <v>19.1556</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.04</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.06560000000000001</v>
+        <v>0.0234</v>
       </c>
       <c r="J186" t="n">
-        <v>-1.1152</v>
+        <v>0.3978</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.79</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1192</v>
+        <v>-0.1168</v>
       </c>
       <c r="J187" t="n">
-        <v>-2.0264</v>
+        <v>-1.9856</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2735</v>
+        <v>-0.2379</v>
       </c>
       <c r="J188" t="n">
-        <v>-4.6495</v>
+        <v>-4.0443</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.38</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.7938</v>
+        <v>-0.5516</v>
       </c>
       <c r="J189" t="n">
-        <v>-13.4946</v>
+        <v>-9.3772</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.25</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.9758</v>
+        <v>-0.6831</v>
       </c>
       <c r="J190" t="n">
-        <v>-16.5886</v>
+        <v>-11.6127</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.24</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.989</v>
+        <v>-0.6935</v>
       </c>
       <c r="J191" t="n">
-        <v>-16.813</v>
+        <v>-11.7895</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.65</v>
       </c>
       <c r="I192" t="n">
-        <v>1.4094</v>
+        <v>1.2792</v>
       </c>
       <c r="J192" t="n">
-        <v>29.5974</v>
+        <v>26.8632</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.48</v>
       </c>
       <c r="I193" t="n">
-        <v>1.0685</v>
+        <v>1.0771</v>
       </c>
       <c r="J193" t="n">
-        <v>22.4385</v>
+        <v>22.6191</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.41</v>
       </c>
       <c r="I194" t="n">
-        <v>0.893</v>
+        <v>0.9811</v>
       </c>
       <c r="J194" t="n">
-        <v>18.753</v>
+        <v>20.6031</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.32</v>
       </c>
       <c r="I195" t="n">
-        <v>0.6849</v>
+        <v>0.7961</v>
       </c>
       <c r="J195" t="n">
-        <v>14.3829</v>
+        <v>16.7181</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.26</v>
       </c>
       <c r="I196" t="n">
-        <v>0.5486</v>
+        <v>0.6592</v>
       </c>
       <c r="J196" t="n">
-        <v>11.5206</v>
+        <v>13.8432</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.08</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2872</v>
+        <v>0.2972</v>
       </c>
       <c r="J197" t="n">
-        <v>6.0312</v>
+        <v>6.2412</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.78</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.3096</v>
+        <v>-0.2311</v>
       </c>
       <c r="J198" t="n">
-        <v>-6.5016</v>
+        <v>-4.8531</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.76</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.3537</v>
+        <v>-0.2494</v>
       </c>
       <c r="J199" t="n">
-        <v>-7.4277</v>
+        <v>-5.2374</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.62</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5706</v>
+        <v>-0.3806</v>
       </c>
       <c r="J200" t="n">
-        <v>-11.9826</v>
+        <v>-7.9926</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.58</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6245000000000001</v>
+        <v>-0.4181</v>
       </c>
       <c r="J201" t="n">
-        <v>-13.1145</v>
+        <v>-8.780099999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.35</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5645</v>
+        <v>0.6805</v>
       </c>
       <c r="J202" t="n">
-        <v>16.935</v>
+        <v>20.415</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.14</v>
       </c>
       <c r="I203" t="n">
-        <v>0.271</v>
+        <v>0.3109</v>
       </c>
       <c r="J203" t="n">
-        <v>8.130000000000001</v>
+        <v>9.327</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.13</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2547</v>
+        <v>0.2919</v>
       </c>
       <c r="J204" t="n">
-        <v>7.641</v>
+        <v>8.757</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.85</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3236</v>
+        <v>-0.1947</v>
       </c>
       <c r="J205" t="n">
-        <v>-9.708</v>
+        <v>-5.841</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.83</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3533</v>
+        <v>-0.2154</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.599</v>
+        <v>-6.462</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.46</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1768</v>
+        <v>1.1078</v>
       </c>
       <c r="J207" t="n">
-        <v>35.304</v>
+        <v>33.234</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.35</v>
       </c>
       <c r="I208" t="n">
-        <v>0.944</v>
+        <v>0.9312</v>
       </c>
       <c r="J208" t="n">
-        <v>28.32</v>
+        <v>27.936</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.27</v>
       </c>
       <c r="I209" t="n">
-        <v>0.7615</v>
+        <v>0.7446</v>
       </c>
       <c r="J209" t="n">
-        <v>22.845</v>
+        <v>22.338</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.79</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-0.6835</v>
       </c>
       <c r="J210" t="n">
-        <v>-22.062</v>
+        <v>-20.505</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.78</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.759</v>
+        <v>-0.7091</v>
       </c>
       <c r="J211" t="n">
-        <v>-22.77</v>
+        <v>-21.273</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.82</v>
       </c>
       <c r="I212" t="n">
-        <v>1.7087</v>
+        <v>1.4721</v>
       </c>
       <c r="J212" t="n">
-        <v>34.174</v>
+        <v>29.442</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.61</v>
       </c>
       <c r="I213" t="n">
-        <v>1.3231</v>
+        <v>1.2287</v>
       </c>
       <c r="J213" t="n">
-        <v>26.462</v>
+        <v>24.574</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.56</v>
       </c>
       <c r="I214" t="n">
-        <v>1.2242</v>
+        <v>1.1697</v>
       </c>
       <c r="J214" t="n">
-        <v>24.484</v>
+        <v>23.394</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.41</v>
       </c>
       <c r="I215" t="n">
-        <v>0.8777</v>
+        <v>0.9785</v>
       </c>
       <c r="J215" t="n">
-        <v>17.554</v>
+        <v>19.57</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.83</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.7079</v>
+        <v>-0.6482</v>
       </c>
       <c r="J216" t="n">
-        <v>-14.158</v>
+        <v>-12.964</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.84</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.1867</v>
+        <v>-0.1627</v>
       </c>
       <c r="J217" t="n">
-        <v>-3.734</v>
+        <v>-3.254</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.2357</v>
+        <v>-0.1947</v>
       </c>
       <c r="J218" t="n">
-        <v>-4.714</v>
+        <v>-3.894</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.74</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3531</v>
+        <v>-0.264</v>
       </c>
       <c r="J219" t="n">
-        <v>-7.062</v>
+        <v>-5.28</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.65</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.5132</v>
+        <v>-0.3464</v>
       </c>
       <c r="J220" t="n">
-        <v>-10.264</v>
+        <v>-6.928</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.58</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6126</v>
+        <v>-0.4118</v>
       </c>
       <c r="J221" t="n">
-        <v>-12.252</v>
+        <v>-8.236000000000001</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>2.18</v>
       </c>
       <c r="I222" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J222" t="n">
-        <v>41.186</v>
+        <v>36.676</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.61</v>
       </c>
       <c r="I223" t="n">
-        <v>1.2891</v>
+        <v>1.2191</v>
       </c>
       <c r="J223" t="n">
-        <v>25.782</v>
+        <v>24.382</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.37</v>
       </c>
       <c r="I224" t="n">
-        <v>0.757</v>
+        <v>0.888</v>
       </c>
       <c r="J224" t="n">
-        <v>15.14</v>
+        <v>17.76</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.32</v>
       </c>
       <c r="I225" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="J225" t="n">
-        <v>12.994</v>
+        <v>15.554</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.11</v>
       </c>
       <c r="I226" t="n">
-        <v>0.1606</v>
+        <v>0.2605</v>
       </c>
       <c r="J226" t="n">
-        <v>3.212</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.93</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.0001</v>
+        <v>-0.0359</v>
       </c>
       <c r="J227" t="n">
-        <v>-0.002</v>
+        <v>-0.718</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.82</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1857</v>
+        <v>-0.1679</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.714</v>
+        <v>-3.358</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.8</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2175</v>
+        <v>-0.1898</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.35</v>
+        <v>-3.796</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.42</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.551</v>
       </c>
       <c r="J230" t="n">
-        <v>-16.078</v>
+        <v>-11.02</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.32</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.9268</v>
+        <v>-0.6453</v>
       </c>
       <c r="J231" t="n">
-        <v>-18.536</v>
+        <v>-12.906</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2573/event_2573_evp_summary.xlsx
+++ b/database/event/2573/event_2573_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.7601</v>
+        <v>7.0202</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8167</v>
+        <v>0.8482</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4138</v>
+        <v>2.5715</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7601</v>
+        <v>7.0202</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4136</v>
+        <v>3.6202</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3465</v>
+        <v>3.4</v>
       </c>
       <c r="H2" t="n">
-        <v>6.5411</v>
+        <v>7.0503</v>
       </c>
       <c r="I2" t="n">
-        <v>3.401</v>
+        <v>3.8071</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3465</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
@@ -529,7 +529,7 @@
         <v>147</v>
       </c>
       <c r="M2" t="n">
-        <v>6.7475</v>
+        <v>7.207100000000001</v>
       </c>
       <c r="N2" t="n">
         <v>184</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.6274</v>
+        <v>5.8153</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.7026</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9025</v>
+        <v>2.023</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6274</v>
+        <v>5.8153</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6569</v>
+        <v>2.5775</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9705</v>
+        <v>3.2378</v>
       </c>
       <c r="H3" t="n">
-        <v>3.875</v>
+        <v>3.6099</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0148</v>
+        <v>1.9493</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9705</v>
+        <v>3.2378</v>
       </c>
       <c r="K3" t="n">
         <v>37</v>
@@ -575,7 +575,7 @@
         <v>147</v>
       </c>
       <c r="M3" t="n">
-        <v>4.985300000000001</v>
+        <v>5.1871</v>
       </c>
       <c r="N3" t="n">
         <v>184</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.2428</v>
+        <v>5.3619</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6334</v>
+        <v>0.6478</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7288</v>
+        <v>1.8166</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2428</v>
+        <v>5.3619</v>
       </c>
       <c r="F4" t="n">
-        <v>4.0892</v>
+        <v>4.1133</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1536</v>
+        <v>1.2486</v>
       </c>
       <c r="H4" t="n">
-        <v>8.9215</v>
+        <v>8.677</v>
       </c>
       <c r="I4" t="n">
-        <v>4.6388</v>
+        <v>4.6855</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1536</v>
+        <v>1.2486</v>
       </c>
       <c r="K4" t="n">
         <v>84</v>
@@ -621,7 +621,7 @@
         <v>96</v>
       </c>
       <c r="M4" t="n">
-        <v>5.7924</v>
+        <v>5.9341</v>
       </c>
       <c r="N4" t="n">
         <v>180</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.357</v>
+        <v>4.3734</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5264</v>
+        <v>0.5284</v>
       </c>
       <c r="D5" t="n">
-        <v>1.329</v>
+        <v>1.3667</v>
       </c>
       <c r="E5" t="n">
-        <v>4.357</v>
+        <v>4.3734</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0506</v>
+        <v>2.9987</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3064</v>
+        <v>1.3747</v>
       </c>
       <c r="H5" t="n">
-        <v>5.2623</v>
+        <v>4.9995</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7361</v>
+        <v>2.6997</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3064</v>
+        <v>1.3747</v>
       </c>
       <c r="K5" t="n">
         <v>47</v>
@@ -667,7 +667,7 @@
         <v>108</v>
       </c>
       <c r="M5" t="n">
-        <v>4.0425</v>
+        <v>4.0744</v>
       </c>
       <c r="N5" t="n">
         <v>155</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3253</v>
+        <v>4.2554</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5226</v>
+        <v>0.5141</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3146</v>
+        <v>1.3129</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3253</v>
+        <v>4.2554</v>
       </c>
       <c r="F6" t="n">
-        <v>3.9232</v>
+        <v>3.8432</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4021</v>
+        <v>0.4122</v>
       </c>
       <c r="H6" t="n">
-        <v>8.336499999999999</v>
+        <v>7.7859</v>
       </c>
       <c r="I6" t="n">
-        <v>4.3346</v>
+        <v>4.2043</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4021</v>
+        <v>0.4122</v>
       </c>
       <c r="K6" t="n">
         <v>84</v>
@@ -713,7 +713,7 @@
         <v>96</v>
       </c>
       <c r="M6" t="n">
-        <v>4.7367</v>
+        <v>4.6165</v>
       </c>
       <c r="N6" t="n">
         <v>180</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0323</v>
+        <v>4.0633</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4872</v>
+        <v>0.4909</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1824</v>
+        <v>1.2255</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0323</v>
+        <v>4.0633</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5407</v>
+        <v>1.5211</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4916</v>
+        <v>2.5422</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5407</v>
+        <v>1.5211</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8011</v>
+        <v>0.8214</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4916</v>
+        <v>2.5422</v>
       </c>
       <c r="K7" t="n">
         <v>37</v>
@@ -759,7 +759,7 @@
         <v>147</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2927</v>
+        <v>3.3636</v>
       </c>
       <c r="N7" t="n">
         <v>184</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0548</v>
+        <v>3.0943</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3691</v>
+        <v>0.3739</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7411</v>
+        <v>0.7844</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0548</v>
+        <v>3.0943</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4061</v>
+        <v>2.3648</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.7295</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9912</v>
+        <v>2.9082</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5553</v>
+        <v>1.5704</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.7295</v>
       </c>
       <c r="K8" t="n">
         <v>37</v>
@@ -805,7 +805,7 @@
         <v>147</v>
       </c>
       <c r="M8" t="n">
-        <v>2.204</v>
+        <v>2.2999</v>
       </c>
       <c r="N8" t="n">
         <v>184</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9416</v>
+        <v>2.8685</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3554</v>
+        <v>0.3466</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6816</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9416</v>
+        <v>2.8685</v>
       </c>
       <c r="F9" t="n">
-        <v>3.101</v>
+        <v>3.0364</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1594</v>
+        <v>-0.1679</v>
       </c>
       <c r="H9" t="n">
-        <v>5.4396</v>
+        <v>5.1242</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8284</v>
+        <v>2.767</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1594</v>
+        <v>-0.1679</v>
       </c>
       <c r="K9" t="n">
         <v>84</v>
@@ -851,7 +851,7 @@
         <v>96</v>
       </c>
       <c r="M9" t="n">
-        <v>2.669</v>
+        <v>2.5991</v>
       </c>
       <c r="N9" t="n">
         <v>180</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8358</v>
+        <v>2.7972</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3426</v>
+        <v>0.338</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6422</v>
+        <v>0.6491</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8358</v>
+        <v>2.7972</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1988</v>
+        <v>3.1219</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.363</v>
+        <v>-0.3247</v>
       </c>
       <c r="H10" t="n">
-        <v>5.7842</v>
+        <v>5.406</v>
       </c>
       <c r="I10" t="n">
-        <v>3.0075</v>
+        <v>2.9192</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.363</v>
+        <v>-0.3247</v>
       </c>
       <c r="K10" t="n">
         <v>84</v>
@@ -897,7 +897,7 @@
         <v>96</v>
       </c>
       <c r="M10" t="n">
-        <v>2.6445</v>
+        <v>2.5945</v>
       </c>
       <c r="N10" t="n">
         <v>180</v>
@@ -906,139 +906,139 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8209</v>
+        <v>2.7394</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3408</v>
+        <v>0.331</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6355</v>
+        <v>0.6228</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8209</v>
+        <v>2.7394</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8209</v>
+        <v>1.4706</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1.2688</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8344</v>
+        <v>1.4706</v>
       </c>
       <c r="I11" t="n">
-        <v>2.951</v>
+        <v>0.7941</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1.2688</v>
       </c>
       <c r="K11" t="n">
-        <v>190</v>
+        <v>84</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M11" t="n">
-        <v>2.951</v>
+        <v>2.0629</v>
       </c>
       <c r="N11" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rickeh</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7174</v>
+        <v>2.6312</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3283</v>
+        <v>0.3179</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5888</v>
+        <v>0.5736</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7174</v>
+        <v>2.6312</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7174</v>
+        <v>2.8962</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.265</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7174</v>
+        <v>4.6614</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8292</v>
+        <v>2.5171</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0.265</v>
       </c>
       <c r="K12" t="n">
-        <v>190</v>
+        <v>37</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8292</v>
+        <v>2.2521</v>
       </c>
       <c r="N12" t="n">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6707</v>
+        <v>2.5413</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3227</v>
+        <v>0.307</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5677</v>
+        <v>0.5326</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6707</v>
+        <v>2.5413</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9472</v>
+        <v>2.5413</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2765</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>4.8979</v>
+        <v>2.8371</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5467</v>
+        <v>2.9102</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2765</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>37</v>
+        <v>190</v>
       </c>
       <c r="L13" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.2702</v>
+        <v>2.9102</v>
       </c>
       <c r="N13" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6383</v>
+        <v>2.5373</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3188</v>
+        <v>0.3066</v>
       </c>
       <c r="D14" t="n">
-        <v>0.553</v>
+        <v>0.5308</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6383</v>
+        <v>2.5373</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4828</v>
+        <v>2.39</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1555</v>
+        <v>0.1473</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2616</v>
+        <v>2.9912</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6959</v>
+        <v>1.6152</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1555</v>
+        <v>0.1473</v>
       </c>
       <c r="K14" t="n">
         <v>129</v>
@@ -1081,7 +1081,7 @@
         <v>57</v>
       </c>
       <c r="M14" t="n">
-        <v>1.8514</v>
+        <v>1.7625</v>
       </c>
       <c r="N14" t="n">
         <v>186</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.6242</v>
+        <v>2.5202</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3171</v>
+        <v>0.3045</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5467</v>
+        <v>0.523</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6242</v>
+        <v>2.5202</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4596</v>
+        <v>2.1398</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1646</v>
+        <v>0.3804</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4596</v>
+        <v>2.1658</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7589</v>
+        <v>1.1695</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1646</v>
+        <v>0.3804</v>
       </c>
       <c r="K15" t="n">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="L15" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9235</v>
+        <v>1.5499</v>
       </c>
       <c r="N15" t="n">
-        <v>180</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>Rickeh</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.5261</v>
+        <v>2.445</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3052</v>
+        <v>0.2954</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5024</v>
+        <v>0.4888</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5261</v>
+        <v>2.445</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2168</v>
+        <v>2.445</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3093</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3242</v>
+        <v>2.6263</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2085</v>
+        <v>2.694</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3093</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>47</v>
+        <v>190</v>
       </c>
       <c r="L16" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.5178</v>
+        <v>2.694</v>
       </c>
       <c r="N16" t="n">
-        <v>155</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3697</v>
+        <v>2.2604</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2863</v>
+        <v>0.2731</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4318</v>
+        <v>0.4048</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3697</v>
+        <v>2.2604</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6715</v>
+        <v>2.5849</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3018</v>
+        <v>-0.3245</v>
       </c>
       <c r="H17" t="n">
-        <v>3.9263</v>
+        <v>3.6343</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0415</v>
+        <v>1.9625</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3018</v>
+        <v>-0.3245</v>
       </c>
       <c r="K17" t="n">
         <v>129</v>
@@ -1219,7 +1219,7 @@
         <v>57</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7397</v>
+        <v>1.638</v>
       </c>
       <c r="N17" t="n">
         <v>186</v>
@@ -1228,47 +1228,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nifty</t>
+          <t>gob b</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.2598</v>
+        <v>2.0873</v>
       </c>
       <c r="C18" t="n">
-        <v>0.273</v>
+        <v>0.2522</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3822</v>
+        <v>0.326</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2598</v>
+        <v>2.0873</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8098</v>
+        <v>1.0511</v>
       </c>
       <c r="G18" t="n">
-        <v>0.45</v>
+        <v>1.0362</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8098</v>
+        <v>1.0511</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.5676</v>
       </c>
       <c r="J18" t="n">
-        <v>0.45</v>
+        <v>1.0362</v>
       </c>
       <c r="K18" t="n">
-        <v>129</v>
+        <v>47</v>
       </c>
       <c r="L18" t="n">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="M18" t="n">
-        <v>1.391</v>
+        <v>1.6038</v>
       </c>
       <c r="N18" t="n">
-        <v>186</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.1495</v>
+        <v>2.0441</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2597</v>
+        <v>0.247</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3324</v>
+        <v>0.3063</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1495</v>
+        <v>2.0441</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4828</v>
+        <v>2.4021</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3333</v>
+        <v>-0.358</v>
       </c>
       <c r="H19" t="n">
-        <v>3.2614</v>
+        <v>3.0312</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6958</v>
+        <v>1.6368</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3333</v>
+        <v>-0.358</v>
       </c>
       <c r="K19" t="n">
         <v>47</v>
@@ -1311,7 +1311,7 @@
         <v>108</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3625</v>
+        <v>1.2788</v>
       </c>
       <c r="N19" t="n">
         <v>155</v>
@@ -1320,47 +1320,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>gob b</t>
+          <t>Nifty</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.1423</v>
+        <v>2.0377</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2588</v>
+        <v>0.2462</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3291</v>
+        <v>0.3034</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1423</v>
+        <v>2.0377</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1395</v>
+        <v>1.5345</v>
       </c>
       <c r="G20" t="n">
-        <v>1.0028</v>
+        <v>0.5032</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1395</v>
+        <v>1.5345</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5925</v>
+        <v>0.8286</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0028</v>
+        <v>0.5032</v>
       </c>
       <c r="K20" t="n">
-        <v>47</v>
+        <v>129</v>
       </c>
       <c r="L20" t="n">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5953</v>
+        <v>1.3318</v>
       </c>
       <c r="N20" t="n">
-        <v>155</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0113</v>
+        <v>2.0315</v>
       </c>
       <c r="C21" t="n">
-        <v>0.243</v>
+        <v>0.2454</v>
       </c>
       <c r="D21" t="n">
-        <v>0.27</v>
+        <v>0.3006</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0113</v>
+        <v>2.0315</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0113</v>
+        <v>2.0315</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0113</v>
+        <v>2.0315</v>
       </c>
       <c r="I21" t="n">
-        <v>2.094</v>
+        <v>2.0839</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.094</v>
+        <v>2.0839</v>
       </c>
       <c r="N21" t="n">
         <v>190</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.9364</v>
+        <v>1.9614</v>
       </c>
       <c r="C22" t="n">
-        <v>0.234</v>
+        <v>0.237</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2362</v>
+        <v>0.2687</v>
       </c>
       <c r="E22" t="n">
-        <v>1.9364</v>
+        <v>1.9614</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9364</v>
+        <v>1.9614</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9364</v>
+        <v>1.9614</v>
       </c>
       <c r="I22" t="n">
-        <v>2.016</v>
+        <v>2.0119</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.016</v>
+        <v>2.0119</v>
       </c>
       <c r="N22" t="n">
         <v>190</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1096</v>
+        <v>1.0288</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1341</v>
+        <v>0.1243</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1371</v>
+        <v>-0.1559</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1096</v>
+        <v>1.0288</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1096</v>
+        <v>1.0288</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1096</v>
+        <v>1.0288</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1096</v>
+        <v>1.0288</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1096</v>
+        <v>1.0288</v>
       </c>
       <c r="N23" t="n">
         <v>79</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4527</v>
+        <v>0.3777</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0547</v>
+        <v>0.0456</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4336</v>
+        <v>-0.4523</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4527</v>
+        <v>0.3777</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4527</v>
+        <v>0.3777</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4527</v>
+        <v>0.3777</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4527</v>
+        <v>0.3777</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4527</v>
+        <v>0.3777</v>
       </c>
       <c r="N24" t="n">
         <v>98</v>
@@ -1550,78 +1550,78 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Maniac</t>
+          <t>FNS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4358</v>
+        <v>0.3676</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0527</v>
+        <v>0.0444</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4413</v>
+        <v>-0.4569</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4358</v>
+        <v>0.3676</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4358</v>
+        <v>0.3676</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4358</v>
+        <v>0.3676</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4358</v>
+        <v>0.3771</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>116</v>
+        <v>190</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4358</v>
+        <v>0.3771</v>
       </c>
       <c r="N25" t="n">
-        <v>116</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ex6TenZ</t>
+          <t>Maniac</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4124</v>
+        <v>0.3169</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0498</v>
+        <v>0.0383</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4518</v>
+        <v>-0.4799</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4124</v>
+        <v>0.3169</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4124</v>
+        <v>0.3169</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4124</v>
+        <v>0.3169</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4124</v>
+        <v>0.3169</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4124</v>
+        <v>0.3169</v>
       </c>
       <c r="N26" t="n">
         <v>116</v>
@@ -1642,47 +1642,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FNS</t>
+          <t>Ex6TenZ</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3055</v>
+        <v>0.2909</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0369</v>
+        <v>0.0351</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5001</v>
+        <v>-0.4918</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3055</v>
+        <v>0.2909</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3055</v>
+        <v>0.2909</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3055</v>
+        <v>0.2909</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3181</v>
+        <v>0.2909</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>190</v>
+        <v>116</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3181</v>
+        <v>0.2909</v>
       </c>
       <c r="N27" t="n">
-        <v>190</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2786</v>
+        <v>0.2219</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0337</v>
+        <v>0.0268</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5122</v>
+        <v>-0.5232</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2786</v>
+        <v>0.2219</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2786</v>
+        <v>0.2219</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2786</v>
+        <v>0.2219</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2786</v>
+        <v>0.2219</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2786</v>
+        <v>0.2219</v>
       </c>
       <c r="N28" t="n">
         <v>98</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0324</v>
+        <v>-0.0476</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0039</v>
+        <v>-0.0058</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6234</v>
+        <v>-0.6459</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0324</v>
+        <v>-0.0476</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0324</v>
+        <v>-0.0476</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0324</v>
+        <v>-0.0476</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0324</v>
+        <v>-0.0476</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0324</v>
+        <v>-0.0476</v>
       </c>
       <c r="N29" t="n">
         <v>116</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1568</v>
+        <v>-0.2037</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0189</v>
+        <v>-0.0246</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7088</v>
+        <v>-0.7169</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1568</v>
+        <v>-0.2037</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1568</v>
+        <v>-0.2037</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1568</v>
+        <v>-0.2037</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1568</v>
+        <v>-0.2037</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1568</v>
+        <v>-0.2037</v>
       </c>
       <c r="N30" t="n">
         <v>79</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2026</v>
+        <v>-0.2348</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0245</v>
+        <v>-0.0284</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7295</v>
+        <v>-0.7311</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2026</v>
+        <v>-0.2348</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2026</v>
+        <v>-0.2348</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2026</v>
+        <v>-0.2348</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2026</v>
+        <v>-0.2348</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2026</v>
+        <v>-0.2348</v>
       </c>
       <c r="N31" t="n">
         <v>79</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2382</v>
+        <v>-0.279</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0288</v>
+        <v>-0.0337</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7455000000000001</v>
+        <v>-0.7512</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2382</v>
+        <v>-0.279</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.2382</v>
+        <v>-0.279</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.2382</v>
+        <v>-0.279</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2382</v>
+        <v>-0.279</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2382</v>
+        <v>-0.279</v>
       </c>
       <c r="N32" t="n">
         <v>79</v>
@@ -1918,93 +1918,93 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ALEX</t>
+          <t>LEGIJA</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3976</v>
+        <v>-0.419</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.048</v>
+        <v>-0.0506</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8175</v>
+        <v>-0.8149</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3976</v>
+        <v>-0.419</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3976</v>
+        <v>-0.1594</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.2596</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3976</v>
+        <v>-0.1594</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3976</v>
+        <v>-0.0861</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.2596</v>
       </c>
       <c r="K33" t="n">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3976</v>
+        <v>-0.3457</v>
       </c>
       <c r="N33" t="n">
-        <v>116</v>
+        <v>155</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LEGIJA</t>
+          <t>ALEX</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5305</v>
+        <v>-0.4535</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0641</v>
+        <v>-0.0548</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.8306</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5305</v>
+        <v>-0.4535</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.2504</v>
+        <v>-0.4535</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.2801</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.2504</v>
+        <v>-0.4535</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1302</v>
+        <v>-0.4535</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.2801</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c r="L34" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4103</v>
+        <v>-0.4535</v>
       </c>
       <c r="N34" t="n">
-        <v>155</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7608</v>
+        <v>-0.7462</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0919</v>
+        <v>-0.0902</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9815</v>
+        <v>-0.9639</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7608</v>
+        <v>-0.7462</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7608</v>
+        <v>-0.7462</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7608</v>
+        <v>-0.7462</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7608</v>
+        <v>-0.7462</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7608</v>
+        <v>-0.7462</v>
       </c>
       <c r="N35" t="n">
         <v>98</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8955</v>
+        <v>-0.945</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1082</v>
+        <v>-0.1142</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0423</v>
+        <v>-1.0544</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8955</v>
+        <v>-0.945</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8955</v>
+        <v>-0.945</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8955</v>
+        <v>-0.945</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8955</v>
+        <v>-0.945</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8955</v>
+        <v>-0.945</v>
       </c>
       <c r="N36" t="n">
         <v>98</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1242</v>
+        <v>-1.1618</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1358</v>
+        <v>-0.1404</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1455</v>
+        <v>-1.1531</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1242</v>
+        <v>-1.1618</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.1242</v>
+        <v>-1.1618</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.1242</v>
+        <v>-1.1618</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1242</v>
+        <v>-1.1618</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1242</v>
+        <v>-1.1618</v>
       </c>
       <c r="N37" t="n">
         <v>79</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.311</v>
+        <v>-1.2354</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1584</v>
+        <v>-0.1493</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2299</v>
+        <v>-1.1866</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.311</v>
+        <v>-1.2354</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.4403</v>
+        <v>-1.3528</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1293</v>
+        <v>0.1174</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.4403</v>
+        <v>-1.3528</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.7489</v>
+        <v>-0.7305</v>
       </c>
       <c r="J38" t="n">
-        <v>0.1293</v>
+        <v>0.1174</v>
       </c>
       <c r="K38" t="n">
         <v>129</v>
@@ -2185,7 +2185,7 @@
         <v>57</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.6196</v>
+        <v>-0.6131</v>
       </c>
       <c r="N38" t="n">
         <v>186</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.4144</v>
+        <v>-1.4601</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1709</v>
+        <v>-0.1764</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2765</v>
+        <v>-1.2889</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4144</v>
+        <v>-1.4601</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4144</v>
+        <v>-1.4601</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.4144</v>
+        <v>-1.4601</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.4144</v>
+        <v>-1.4601</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.4144</v>
+        <v>-1.4601</v>
       </c>
       <c r="N39" t="n">
         <v>98</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.9605</v>
+        <v>-1.957</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2369</v>
+        <v>-0.2364</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5231</v>
+        <v>-1.5151</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.9605</v>
+        <v>-1.957</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.9605</v>
+        <v>-1.957</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.9605</v>
+        <v>-1.957</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.9605</v>
+        <v>-1.957</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.9605</v>
+        <v>-1.957</v>
       </c>
       <c r="N40" t="n">
         <v>116</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.0771</v>
+        <v>-2.8497</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3718</v>
+        <v>-0.3443</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.0272</v>
+        <v>-1.9214</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.0771</v>
+        <v>-2.8497</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.1878</v>
+        <v>-2.9623</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1107</v>
+        <v>0.1126</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.1878</v>
+        <v>-2.9623</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.6575</v>
+        <v>-1.5996</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1107</v>
+        <v>0.1126</v>
       </c>
       <c r="K41" t="n">
         <v>129</v>
@@ -2323,7 +2323,7 @@
         <v>57</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.5468</v>
+        <v>-1.487</v>
       </c>
       <c r="N41" t="n">
         <v>186</v>
@@ -2429,10 +2429,10 @@
         <v>1.28</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5988</v>
+        <v>0.5778</v>
       </c>
       <c r="J2" t="n">
-        <v>17.3652</v>
+        <v>16.7562</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.19</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4345</v>
+        <v>0.427</v>
       </c>
       <c r="J3" t="n">
-        <v>12.6005</v>
+        <v>12.383</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.11</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2784</v>
+        <v>0.2805</v>
       </c>
       <c r="J4" t="n">
-        <v>8.073600000000001</v>
+        <v>8.134499999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.61</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4155</v>
+        <v>-0.4249</v>
       </c>
       <c r="J5" t="n">
-        <v>-12.0495</v>
+        <v>-12.3221</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.6</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4247</v>
+        <v>-0.4337</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.3163</v>
+        <v>-12.5773</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.62</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2925</v>
+        <v>1.3578</v>
       </c>
       <c r="J7" t="n">
-        <v>37.4825</v>
+        <v>39.3762</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.3</v>
       </c>
       <c r="I8" t="n">
-        <v>0.793</v>
+        <v>0.7526</v>
       </c>
       <c r="J8" t="n">
-        <v>22.997</v>
+        <v>21.8254</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4622</v>
+        <v>0.4565</v>
       </c>
       <c r="J9" t="n">
-        <v>13.4038</v>
+        <v>13.2385</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.02</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0469</v>
+        <v>0.0673</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3601</v>
+        <v>1.9517</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.91</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3747</v>
+        <v>-0.3535</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.8663</v>
+        <v>-10.2515</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.89</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1004</v>
+        <v>-0.1235</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.2088</v>
+        <v>-2.717</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.83</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1686</v>
+        <v>-0.1913</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.7092</v>
+        <v>-4.2086</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.77</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2313</v>
+        <v>-0.2529</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.0886</v>
+        <v>-5.5638</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.62</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3709</v>
+        <v>-0.3883</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.159800000000001</v>
+        <v>-8.5426</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.4</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5764</v>
+        <v>-0.5813</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.6808</v>
+        <v>-12.7886</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.69</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3218</v>
+        <v>1.4127</v>
       </c>
       <c r="J17" t="n">
-        <v>29.0796</v>
+        <v>31.0794</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.5</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0982</v>
+        <v>1.0885</v>
       </c>
       <c r="J18" t="n">
-        <v>24.1604</v>
+        <v>23.947</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.46</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0504</v>
+        <v>1.0188</v>
       </c>
       <c r="J19" t="n">
-        <v>23.1088</v>
+        <v>22.4136</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.45</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0378</v>
+        <v>1.0014</v>
       </c>
       <c r="J20" t="n">
-        <v>22.8316</v>
+        <v>22.0308</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.14</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3562</v>
+        <v>0.3717</v>
       </c>
       <c r="J21" t="n">
-        <v>7.8364</v>
+        <v>8.1774</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.5</v>
       </c>
       <c r="I22" t="n">
-        <v>0.892</v>
+        <v>0.9784</v>
       </c>
       <c r="J22" t="n">
-        <v>26.76</v>
+        <v>29.352</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.15</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4039</v>
+        <v>0.4405</v>
       </c>
       <c r="J23" t="n">
-        <v>12.117</v>
+        <v>13.215</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.15</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4039</v>
+        <v>0.4405</v>
       </c>
       <c r="J24" t="n">
-        <v>12.117</v>
+        <v>13.215</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.96</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1941</v>
+        <v>-0.1893</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.823</v>
+        <v>-5.679</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.8</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.653</v>
+        <v>-0.6098</v>
       </c>
       <c r="J26" t="n">
-        <v>-19.59</v>
+        <v>-18.294</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.21</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4031</v>
+        <v>0.4426</v>
       </c>
       <c r="J27" t="n">
-        <v>12.093</v>
+        <v>13.278</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.19</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3816</v>
+        <v>0.4121</v>
       </c>
       <c r="J28" t="n">
-        <v>11.448</v>
+        <v>12.363</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.11</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2622</v>
+        <v>0.2687</v>
       </c>
       <c r="J29" t="n">
-        <v>7.866</v>
+        <v>8.061</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.84</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2004</v>
+        <v>-0.2135</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.012</v>
+        <v>-6.405</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.74</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3</v>
+        <v>-0.312</v>
       </c>
       <c r="J31" t="n">
-        <v>-9</v>
+        <v>-9.359999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.2</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3564</v>
+        <v>0.367</v>
       </c>
       <c r="J32" t="n">
-        <v>9.266400000000001</v>
+        <v>9.542</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0205</v>
+        <v>0.0151</v>
       </c>
       <c r="J33" t="n">
-        <v>0.533</v>
+        <v>0.3926</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.91</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1117</v>
+        <v>-0.1268</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.9042</v>
+        <v>-3.2968</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.67</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.35</v>
+        <v>-0.3637</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.1</v>
+        <v>-9.456200000000001</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.62</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3969</v>
+        <v>-0.4087</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.3194</v>
+        <v>-10.6262</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.37</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4162</v>
+        <v>0.4729</v>
       </c>
       <c r="J37" t="n">
-        <v>10.8212</v>
+        <v>12.2954</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.24</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3239</v>
+        <v>0.3431</v>
       </c>
       <c r="J38" t="n">
-        <v>8.4214</v>
+        <v>8.9206</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.22</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3027</v>
+        <v>0.3205</v>
       </c>
       <c r="J39" t="n">
-        <v>7.8702</v>
+        <v>8.333</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.21</v>
       </c>
       <c r="I40" t="n">
-        <v>0.291</v>
+        <v>0.3089</v>
       </c>
       <c r="J40" t="n">
-        <v>7.566</v>
+        <v>8.0314</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.14</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2028</v>
+        <v>0.2219</v>
       </c>
       <c r="J41" t="n">
-        <v>5.2728</v>
+        <v>5.7694</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.46</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8215</v>
+        <v>0.9062</v>
       </c>
       <c r="J42" t="n">
-        <v>32.86</v>
+        <v>36.248</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.4</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7428</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>29.712</v>
+        <v>32.844</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.27</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5672</v>
+        <v>0.6287</v>
       </c>
       <c r="J44" t="n">
-        <v>22.688</v>
+        <v>25.148</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.043</v>
+        <v>-0.0297</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.72</v>
+        <v>-1.188</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.76</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7716</v>
+        <v>-0.7118</v>
       </c>
       <c r="J46" t="n">
-        <v>-30.864</v>
+        <v>-28.472</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.25</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4588</v>
+        <v>0.5057</v>
       </c>
       <c r="J47" t="n">
-        <v>18.352</v>
+        <v>20.228</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.24</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4481</v>
+        <v>0.4934</v>
       </c>
       <c r="J48" t="n">
-        <v>17.924</v>
+        <v>19.736</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.88</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1511</v>
+        <v>-0.1654</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.044</v>
+        <v>-6.616</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.87</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1618</v>
+        <v>-0.1763</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.472</v>
+        <v>-7.052</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.54</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4792</v>
+        <v>-0.4856</v>
       </c>
       <c r="J51" t="n">
-        <v>-19.168</v>
+        <v>-19.424</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.36</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6819</v>
+        <v>0.7565</v>
       </c>
       <c r="J52" t="n">
-        <v>18.4113</v>
+        <v>20.4255</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.29</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5884</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>15.8868</v>
+        <v>17.6499</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.2</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4659</v>
+        <v>0.5162</v>
       </c>
       <c r="J54" t="n">
-        <v>12.5793</v>
+        <v>13.9374</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.13</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3615</v>
+        <v>0.383</v>
       </c>
       <c r="J55" t="n">
-        <v>9.7605</v>
+        <v>10.341</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.11</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3243</v>
+        <v>0.3331</v>
       </c>
       <c r="J56" t="n">
-        <v>8.7561</v>
+        <v>8.9937</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.12</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3031</v>
+        <v>0.303</v>
       </c>
       <c r="J57" t="n">
-        <v>8.1837</v>
+        <v>8.180999999999999</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.1</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2622</v>
+        <v>0.2639</v>
       </c>
       <c r="J58" t="n">
-        <v>7.0794</v>
+        <v>7.1253</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.91</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1171</v>
+        <v>-0.1309</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.1617</v>
+        <v>-3.5343</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.8</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2323</v>
+        <v>-0.2472</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.2721</v>
+        <v>-6.6744</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.79</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2423</v>
+        <v>-0.2571</v>
       </c>
       <c r="J61" t="n">
-        <v>-6.5421</v>
+        <v>-6.9417</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.21</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5064</v>
+        <v>0.555</v>
       </c>
       <c r="J62" t="n">
-        <v>15.192</v>
+        <v>16.65</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.11</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3503</v>
+        <v>0.3574</v>
       </c>
       <c r="J63" t="n">
-        <v>10.509</v>
+        <v>10.722</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.05</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1865</v>
+        <v>0.193</v>
       </c>
       <c r="J64" t="n">
-        <v>5.595</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.99</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.0643</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="J65" t="n">
-        <v>-1.929</v>
+        <v>-1.983</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.88</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4197</v>
+        <v>-0.4037</v>
       </c>
       <c r="J66" t="n">
-        <v>-12.591</v>
+        <v>-12.111</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.38</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5671</v>
+        <v>0.6341</v>
       </c>
       <c r="J67" t="n">
-        <v>17.013</v>
+        <v>19.023</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.17</v>
       </c>
       <c r="I68" t="n">
-        <v>0.353</v>
+        <v>0.3697</v>
       </c>
       <c r="J68" t="n">
-        <v>10.59</v>
+        <v>11.091</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.96</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.085</v>
+        <v>-2.319</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.93</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1067</v>
+        <v>-0.1166</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.201</v>
+        <v>-3.498</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.87</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1738</v>
+        <v>-0.1856</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.214</v>
+        <v>-5.568</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.83</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4515</v>
+        <v>1.4498</v>
       </c>
       <c r="J72" t="n">
-        <v>26.127</v>
+        <v>26.0964</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.73</v>
       </c>
       <c r="I73" t="n">
-        <v>1.3414</v>
+        <v>1.3325</v>
       </c>
       <c r="J73" t="n">
-        <v>24.1452</v>
+        <v>23.985</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.71</v>
       </c>
       <c r="I74" t="n">
-        <v>1.3193</v>
+        <v>1.3089</v>
       </c>
       <c r="J74" t="n">
-        <v>23.7474</v>
+        <v>23.5602</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.57</v>
       </c>
       <c r="I75" t="n">
-        <v>1.1642</v>
+        <v>1.1416</v>
       </c>
       <c r="J75" t="n">
-        <v>20.9556</v>
+        <v>20.5488</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.33</v>
       </c>
       <c r="I76" t="n">
-        <v>0.778</v>
+        <v>0.7551</v>
       </c>
       <c r="J76" t="n">
-        <v>14.004</v>
+        <v>13.5918</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.42</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.4929</v>
+        <v>-0.5134</v>
       </c>
       <c r="J77" t="n">
-        <v>-8.872199999999999</v>
+        <v>-9.241199999999999</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.4</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.5124</v>
+        <v>-0.5313</v>
       </c>
       <c r="J78" t="n">
-        <v>-9.2232</v>
+        <v>-9.5634</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.37</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.539</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="J79" t="n">
-        <v>-9.702</v>
+        <v>-10.0062</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.37</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.539</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.702</v>
+        <v>-10.0062</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.36</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5484</v>
+        <v>-0.5645</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.8712</v>
+        <v>-10.161</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>2.2</v>
       </c>
       <c r="I82" t="n">
-        <v>1.8338</v>
+        <v>1.8963</v>
       </c>
       <c r="J82" t="n">
-        <v>36.676</v>
+        <v>37.926</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.47</v>
       </c>
       <c r="I83" t="n">
-        <v>1.0589</v>
+        <v>1.0214</v>
       </c>
       <c r="J83" t="n">
-        <v>21.178</v>
+        <v>20.428</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.3</v>
       </c>
       <c r="I84" t="n">
-        <v>0.7357</v>
+        <v>0.7133</v>
       </c>
       <c r="J84" t="n">
-        <v>14.714</v>
+        <v>14.266</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.3</v>
       </c>
       <c r="I85" t="n">
-        <v>0.7357</v>
+        <v>0.7133</v>
       </c>
       <c r="J85" t="n">
-        <v>14.714</v>
+        <v>14.266</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.24</v>
       </c>
       <c r="I86" t="n">
-        <v>0.596</v>
+        <v>0.5896</v>
       </c>
       <c r="J86" t="n">
-        <v>11.92</v>
+        <v>11.792</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.88</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.1111</v>
+        <v>-0.1345</v>
       </c>
       <c r="J87" t="n">
-        <v>-2.222</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.78</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2204</v>
+        <v>-0.2423</v>
       </c>
       <c r="J88" t="n">
-        <v>-4.408</v>
+        <v>-4.846</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.73</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2698</v>
+        <v>-0.2905</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.396</v>
+        <v>-5.81</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.68</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3149</v>
+        <v>-0.3346</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.298</v>
+        <v>-6.692</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.42</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5572</v>
+        <v>-0.5635</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.144</v>
+        <v>-11.27</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.47</v>
       </c>
       <c r="I92" t="n">
-        <v>1.1238</v>
+        <v>1.0812</v>
       </c>
       <c r="J92" t="n">
-        <v>32.5902</v>
+        <v>31.3548</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.16</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4764</v>
+        <v>0.4661</v>
       </c>
       <c r="J93" t="n">
-        <v>13.8156</v>
+        <v>13.5169</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.08</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2634</v>
+        <v>0.2695</v>
       </c>
       <c r="J94" t="n">
-        <v>7.6386</v>
+        <v>7.8155</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.95</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2296</v>
+        <v>-0.2227</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.6584</v>
+        <v>-6.4583</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2618</v>
+        <v>-0.2532</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.5922</v>
+        <v>-7.3428</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.22</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4694</v>
+        <v>0.4632</v>
       </c>
       <c r="J97" t="n">
-        <v>13.6126</v>
+        <v>13.4328</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.21</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4513</v>
+        <v>0.4465</v>
       </c>
       <c r="J98" t="n">
-        <v>13.0877</v>
+        <v>12.9485</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.08</v>
       </c>
       <c r="I99" t="n">
-        <v>0.201</v>
+        <v>0.2096</v>
       </c>
       <c r="J99" t="n">
-        <v>5.829</v>
+        <v>6.0784</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.8</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2411</v>
+        <v>-0.254</v>
       </c>
       <c r="J100" t="n">
-        <v>-6.9919</v>
+        <v>-7.366</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.78</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.261</v>
+        <v>-0.2737</v>
       </c>
       <c r="J101" t="n">
-        <v>-7.569</v>
+        <v>-7.9373</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.26</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4207</v>
+        <v>0.4194</v>
       </c>
       <c r="J102" t="n">
-        <v>10.9382</v>
+        <v>10.9044</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.17</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2949</v>
+        <v>0.3004</v>
       </c>
       <c r="J103" t="n">
-        <v>7.6674</v>
+        <v>7.8104</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.91</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1222</v>
+        <v>-0.1347</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.1772</v>
+        <v>-3.5022</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.85</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.187</v>
+        <v>-0.2008</v>
       </c>
       <c r="J105" t="n">
-        <v>-4.862</v>
+        <v>-5.2208</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.77</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2678</v>
+        <v>-0.281</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.9628</v>
+        <v>-7.306</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.29</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3915</v>
+        <v>0.405</v>
       </c>
       <c r="J107" t="n">
-        <v>10.179</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.23</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3202</v>
+        <v>0.3362</v>
       </c>
       <c r="J108" t="n">
-        <v>8.325200000000001</v>
+        <v>8.741199999999999</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.15</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2226</v>
+        <v>0.2399</v>
       </c>
       <c r="J109" t="n">
-        <v>5.7876</v>
+        <v>6.2374</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.12</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1831</v>
+        <v>0.2005</v>
       </c>
       <c r="J110" t="n">
-        <v>4.7606</v>
+        <v>5.213</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.07</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1115</v>
+        <v>0.128</v>
       </c>
       <c r="J111" t="n">
-        <v>2.899</v>
+        <v>3.328</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.46</v>
       </c>
       <c r="I112" t="n">
-        <v>1.1095</v>
+        <v>1.0657</v>
       </c>
       <c r="J112" t="n">
-        <v>29.9565</v>
+        <v>28.7739</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.06</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2025</v>
+        <v>0.2124</v>
       </c>
       <c r="J113" t="n">
-        <v>5.4675</v>
+        <v>5.7348</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.05</v>
       </c>
       <c r="I114" t="n">
-        <v>0.171</v>
+        <v>0.1824</v>
       </c>
       <c r="J114" t="n">
-        <v>4.617</v>
+        <v>4.9248</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.03</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1035</v>
+        <v>0.1174</v>
       </c>
       <c r="J115" t="n">
-        <v>2.7945</v>
+        <v>3.1698</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.02</v>
       </c>
       <c r="I116" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.081</v>
       </c>
       <c r="J116" t="n">
-        <v>1.7982</v>
+        <v>2.187</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.33</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6511</v>
+        <v>0.6312</v>
       </c>
       <c r="J117" t="n">
-        <v>17.5797</v>
+        <v>17.0424</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.07</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1745</v>
+        <v>0.1851</v>
       </c>
       <c r="J118" t="n">
-        <v>4.7115</v>
+        <v>4.9977</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.06</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1533</v>
+        <v>0.1641</v>
       </c>
       <c r="J119" t="n">
-        <v>4.1391</v>
+        <v>4.4307</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.06</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1533</v>
+        <v>0.1641</v>
       </c>
       <c r="J120" t="n">
-        <v>4.1391</v>
+        <v>4.4307</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.72</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3225</v>
+        <v>-0.3333</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.7075</v>
+        <v>-8.9991</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.22</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6208</v>
+        <v>0.5969</v>
       </c>
       <c r="J122" t="n">
-        <v>18.624</v>
+        <v>17.907</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.19</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5471</v>
+        <v>0.531</v>
       </c>
       <c r="J123" t="n">
-        <v>16.413</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.18</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5223</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="J124" t="n">
-        <v>15.669</v>
+        <v>15.258</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.18</v>
       </c>
       <c r="I125" t="n">
-        <v>0.5223</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="J125" t="n">
-        <v>15.669</v>
+        <v>15.258</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.93</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2984</v>
+        <v>-0.2863</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.952</v>
+        <v>-8.589</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.21</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4828</v>
+        <v>0.4696</v>
       </c>
       <c r="J127" t="n">
-        <v>14.484</v>
+        <v>14.088</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.16</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3874</v>
+        <v>0.3812</v>
       </c>
       <c r="J128" t="n">
-        <v>11.622</v>
+        <v>11.436</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.8</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2306</v>
+        <v>-0.2459</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.918</v>
+        <v>-7.377</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.79</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2406</v>
+        <v>-0.2557</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.218</v>
+        <v>-7.671</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3375</v>
+        <v>-0.3504</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.125</v>
+        <v>-10.512</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.42</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0459</v>
+        <v>0.9933</v>
       </c>
       <c r="J132" t="n">
-        <v>29.2852</v>
+        <v>27.8124</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.29</v>
       </c>
       <c r="I133" t="n">
-        <v>0.7815</v>
+        <v>0.7403</v>
       </c>
       <c r="J133" t="n">
-        <v>21.882</v>
+        <v>20.7284</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.28</v>
       </c>
       <c r="I134" t="n">
-        <v>0.758</v>
+        <v>0.7197</v>
       </c>
       <c r="J134" t="n">
-        <v>21.224</v>
+        <v>20.1516</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.04</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1287</v>
+        <v>0.1444</v>
       </c>
       <c r="J135" t="n">
-        <v>3.6036</v>
+        <v>4.0432</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.78</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.6644</v>
       </c>
       <c r="J136" t="n">
-        <v>-20.0816</v>
+        <v>-18.6032</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.5</v>
       </c>
       <c r="I137" t="n">
-        <v>0.9716</v>
+        <v>0.9164</v>
       </c>
       <c r="J137" t="n">
-        <v>27.2048</v>
+        <v>25.6592</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.1</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2591</v>
+        <v>0.2617</v>
       </c>
       <c r="J138" t="n">
-        <v>7.2548</v>
+        <v>7.3276</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.82</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2134</v>
+        <v>-0.2281</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.9752</v>
+        <v>-6.3868</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3404</v>
+        <v>-0.3527</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.5312</v>
+        <v>-9.8756</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.66</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3686</v>
+        <v>-0.3799</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.3208</v>
+        <v>-10.6372</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.1</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2694</v>
+        <v>0.2692</v>
       </c>
       <c r="J142" t="n">
-        <v>7.8126</v>
+        <v>7.8068</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.99</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.0132</v>
+        <v>-0.0196</v>
       </c>
       <c r="J143" t="n">
-        <v>-0.3828</v>
+        <v>-0.5684</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.91</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1151</v>
+        <v>-0.1294</v>
       </c>
       <c r="J144" t="n">
-        <v>-3.3379</v>
+        <v>-3.7526</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.89</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1368</v>
+        <v>-0.1517</v>
       </c>
       <c r="J145" t="n">
-        <v>-3.9672</v>
+        <v>-4.3993</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.72</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3079</v>
+        <v>-0.3218</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.9291</v>
+        <v>-9.3322</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.33</v>
       </c>
       <c r="I147" t="n">
-        <v>0.8718</v>
+        <v>0.8198</v>
       </c>
       <c r="J147" t="n">
-        <v>25.2822</v>
+        <v>23.7742</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.24</v>
       </c>
       <c r="I148" t="n">
-        <v>0.6611</v>
+        <v>0.6344</v>
       </c>
       <c r="J148" t="n">
-        <v>19.1719</v>
+        <v>18.3976</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.19</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5407</v>
+        <v>0.5266</v>
       </c>
       <c r="J149" t="n">
-        <v>15.6803</v>
+        <v>15.2714</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.05</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1597</v>
+        <v>0.1746</v>
       </c>
       <c r="J150" t="n">
-        <v>4.6313</v>
+        <v>5.0634</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.04</v>
       </c>
       <c r="I151" t="n">
-        <v>0.1267</v>
+        <v>0.143</v>
       </c>
       <c r="J151" t="n">
-        <v>3.6743</v>
+        <v>4.147</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.46</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5988</v>
+        <v>0.5987</v>
       </c>
       <c r="J152" t="n">
-        <v>17.3652</v>
+        <v>17.3623</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.17</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2531</v>
+        <v>0.2689</v>
       </c>
       <c r="J153" t="n">
-        <v>7.3399</v>
+        <v>7.7981</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.13</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2013</v>
+        <v>0.2174</v>
       </c>
       <c r="J154" t="n">
-        <v>5.8377</v>
+        <v>6.3046</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.92</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1239</v>
+        <v>-0.1331</v>
       </c>
       <c r="J155" t="n">
-        <v>-3.5931</v>
+        <v>-3.8599</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.89</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.1577</v>
+        <v>-0.1679</v>
       </c>
       <c r="J156" t="n">
-        <v>-4.5733</v>
+        <v>-4.8691</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.08</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1572</v>
+        <v>0.1666</v>
       </c>
       <c r="J157" t="n">
-        <v>4.5588</v>
+        <v>4.8314</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.08</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1572</v>
+        <v>0.1666</v>
       </c>
       <c r="J158" t="n">
-        <v>4.5588</v>
+        <v>4.8314</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.03</v>
       </c>
       <c r="I159" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0785</v>
       </c>
       <c r="J159" t="n">
-        <v>2.0445</v>
+        <v>2.2765</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.99</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.0204</v>
+        <v>-0.0251</v>
       </c>
       <c r="J160" t="n">
-        <v>-0.5916</v>
+        <v>-0.7279</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2287</v>
+        <v>-0.2423</v>
       </c>
       <c r="J161" t="n">
-        <v>-6.6323</v>
+        <v>-7.0267</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.08</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3603</v>
+        <v>0.3269</v>
       </c>
       <c r="J162" t="n">
-        <v>7.206</v>
+        <v>6.538</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>0.0266</v>
+        <v>-0.0078</v>
       </c>
       <c r="J163" t="n">
-        <v>0.532</v>
+        <v>-0.156</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.55</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.4316</v>
+        <v>-0.4466</v>
       </c>
       <c r="J164" t="n">
-        <v>-8.632</v>
+        <v>-8.932</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.44</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.5432</v>
       </c>
       <c r="J165" t="n">
-        <v>-10.696</v>
+        <v>-10.864</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.33</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.638</v>
+        <v>-0.6387</v>
       </c>
       <c r="J166" t="n">
-        <v>-12.76</v>
+        <v>-12.774</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.68</v>
       </c>
       <c r="I167" t="n">
-        <v>1.3174</v>
+        <v>1.3006</v>
       </c>
       <c r="J167" t="n">
-        <v>26.348</v>
+        <v>26.012</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.57</v>
       </c>
       <c r="I168" t="n">
-        <v>1.1871</v>
+        <v>1.1612</v>
       </c>
       <c r="J168" t="n">
-        <v>23.742</v>
+        <v>23.224</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.47</v>
       </c>
       <c r="I169" t="n">
-        <v>1.0668</v>
+        <v>1.0287</v>
       </c>
       <c r="J169" t="n">
-        <v>21.336</v>
+        <v>20.574</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.37</v>
       </c>
       <c r="I170" t="n">
-        <v>0.9076</v>
+        <v>0.8613</v>
       </c>
       <c r="J170" t="n">
-        <v>18.152</v>
+        <v>17.226</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.95</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2978</v>
+        <v>-0.2706</v>
       </c>
       <c r="J171" t="n">
-        <v>-5.956</v>
+        <v>-5.412</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.45</v>
       </c>
       <c r="I172" t="n">
-        <v>0.8828</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="J172" t="n">
-        <v>22.9528</v>
+        <v>21.6892</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.07</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1893</v>
+        <v>0.1957</v>
       </c>
       <c r="J173" t="n">
-        <v>4.9218</v>
+        <v>5.0882</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.97</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0481</v>
+        <v>-0.0567</v>
       </c>
       <c r="J174" t="n">
-        <v>-1.2506</v>
+        <v>-1.4742</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1534</v>
+        <v>-0.1672</v>
       </c>
       <c r="J175" t="n">
-        <v>-3.9884</v>
+        <v>-4.3472</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.51</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5082</v>
+        <v>-0.5127</v>
       </c>
       <c r="J176" t="n">
-        <v>-13.2132</v>
+        <v>-13.3302</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.74</v>
       </c>
       <c r="I177" t="n">
-        <v>1.4599</v>
+        <v>1.4392</v>
       </c>
       <c r="J177" t="n">
-        <v>37.9574</v>
+        <v>37.4192</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.22</v>
       </c>
       <c r="I178" t="n">
-        <v>0.6187</v>
+        <v>0.5955</v>
       </c>
       <c r="J178" t="n">
-        <v>16.0862</v>
+        <v>15.483</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.07</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2274</v>
+        <v>0.2373</v>
       </c>
       <c r="J179" t="n">
-        <v>5.9124</v>
+        <v>6.1698</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.96</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2036</v>
+        <v>-0.196</v>
       </c>
       <c r="J180" t="n">
-        <v>-5.2936</v>
+        <v>-5.096</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.75</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.7894</v>
+        <v>-0.7287</v>
       </c>
       <c r="J181" t="n">
-        <v>-20.5244</v>
+        <v>-18.9462</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>2.32</v>
       </c>
       <c r="I182" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J182" t="n">
-        <v>31.1746</v>
+        <v>32.9324</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.72</v>
       </c>
       <c r="I183" t="n">
-        <v>1.3276</v>
+        <v>1.3184</v>
       </c>
       <c r="J183" t="n">
-        <v>22.5692</v>
+        <v>22.4128</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.69</v>
       </c>
       <c r="I184" t="n">
-        <v>1.2948</v>
+        <v>1.2832</v>
       </c>
       <c r="J184" t="n">
-        <v>22.0116</v>
+        <v>21.8144</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.54</v>
       </c>
       <c r="I185" t="n">
-        <v>1.1268</v>
+        <v>1.1017</v>
       </c>
       <c r="J185" t="n">
-        <v>19.1556</v>
+        <v>18.7289</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.04</v>
       </c>
       <c r="I186" t="n">
-        <v>0.0234</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="J186" t="n">
-        <v>0.3978</v>
+        <v>1.1985</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.79</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1168</v>
+        <v>-0.1586</v>
       </c>
       <c r="J187" t="n">
-        <v>-1.9856</v>
+        <v>-2.6962</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2379</v>
+        <v>-0.2727</v>
       </c>
       <c r="J188" t="n">
-        <v>-4.0443</v>
+        <v>-4.6359</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.38</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.5516</v>
+        <v>-0.5643</v>
       </c>
       <c r="J189" t="n">
-        <v>-9.3772</v>
+        <v>-9.5931</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.25</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.6831</v>
+        <v>-0.6838</v>
       </c>
       <c r="J190" t="n">
-        <v>-11.6127</v>
+        <v>-11.6246</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.24</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6935</v>
+        <v>-0.6931</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.7895</v>
+        <v>-11.7827</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.65</v>
       </c>
       <c r="I192" t="n">
-        <v>1.2792</v>
+        <v>1.2605</v>
       </c>
       <c r="J192" t="n">
-        <v>26.8632</v>
+        <v>26.4705</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.48</v>
       </c>
       <c r="I193" t="n">
-        <v>1.0771</v>
+        <v>1.0413</v>
       </c>
       <c r="J193" t="n">
-        <v>22.6191</v>
+        <v>21.8673</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.41</v>
       </c>
       <c r="I194" t="n">
-        <v>0.9811</v>
+        <v>0.9322</v>
       </c>
       <c r="J194" t="n">
-        <v>20.6031</v>
+        <v>19.5762</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.32</v>
       </c>
       <c r="I195" t="n">
-        <v>0.7961</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="J195" t="n">
-        <v>16.7181</v>
+        <v>16.0356</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.26</v>
       </c>
       <c r="I196" t="n">
-        <v>0.6592</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="J196" t="n">
-        <v>13.8432</v>
+        <v>13.4946</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.08</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2972</v>
+        <v>0.2801</v>
       </c>
       <c r="J197" t="n">
-        <v>6.2412</v>
+        <v>5.8821</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.78</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.2311</v>
+        <v>-0.2506</v>
       </c>
       <c r="J198" t="n">
-        <v>-4.8531</v>
+        <v>-5.2626</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.76</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2494</v>
+        <v>-0.2688</v>
       </c>
       <c r="J199" t="n">
-        <v>-5.2374</v>
+        <v>-5.6448</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.62</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3806</v>
+        <v>-0.3959</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.9926</v>
+        <v>-8.3139</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.58</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4181</v>
+        <v>-0.4315</v>
       </c>
       <c r="J201" t="n">
-        <v>-8.780099999999999</v>
+        <v>-9.061500000000001</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.35</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6805</v>
+        <v>0.6586</v>
       </c>
       <c r="J202" t="n">
-        <v>20.415</v>
+        <v>19.758</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.14</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3109</v>
+        <v>0.3173</v>
       </c>
       <c r="J203" t="n">
-        <v>9.327</v>
+        <v>9.519</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.13</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2919</v>
+        <v>0.2992</v>
       </c>
       <c r="J204" t="n">
-        <v>8.757</v>
+        <v>8.976000000000001</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.85</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1947</v>
+        <v>-0.2068</v>
       </c>
       <c r="J205" t="n">
-        <v>-5.841</v>
+        <v>-6.204</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.83</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2154</v>
+        <v>-0.2275</v>
       </c>
       <c r="J206" t="n">
-        <v>-6.462</v>
+        <v>-6.825</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.46</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1078</v>
+        <v>1.0642</v>
       </c>
       <c r="J207" t="n">
-        <v>33.234</v>
+        <v>31.926</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.35</v>
       </c>
       <c r="I208" t="n">
-        <v>0.9312</v>
+        <v>0.8702</v>
       </c>
       <c r="J208" t="n">
-        <v>27.936</v>
+        <v>26.106</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.27</v>
       </c>
       <c r="I209" t="n">
-        <v>0.7446</v>
+        <v>0.7059</v>
       </c>
       <c r="J209" t="n">
-        <v>22.338</v>
+        <v>21.177</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.79</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.6835</v>
+        <v>-0.636</v>
       </c>
       <c r="J210" t="n">
-        <v>-20.505</v>
+        <v>-19.08</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.78</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.7091</v>
+        <v>-0.6587</v>
       </c>
       <c r="J211" t="n">
-        <v>-21.273</v>
+        <v>-19.761</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.82</v>
       </c>
       <c r="I212" t="n">
-        <v>1.4721</v>
+        <v>1.4658</v>
       </c>
       <c r="J212" t="n">
-        <v>29.442</v>
+        <v>29.316</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.61</v>
       </c>
       <c r="I213" t="n">
-        <v>1.2287</v>
+        <v>1.2071</v>
       </c>
       <c r="J213" t="n">
-        <v>24.574</v>
+        <v>24.142</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.56</v>
       </c>
       <c r="I214" t="n">
-        <v>1.1697</v>
+        <v>1.1437</v>
       </c>
       <c r="J214" t="n">
-        <v>23.394</v>
+        <v>22.874</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.41</v>
       </c>
       <c r="I215" t="n">
-        <v>0.9785</v>
+        <v>0.9301</v>
       </c>
       <c r="J215" t="n">
-        <v>19.57</v>
+        <v>18.602</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.83</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6482</v>
+        <v>-0.5917</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.964</v>
+        <v>-11.834</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.84</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.1627</v>
+        <v>-0.1845</v>
       </c>
       <c r="J217" t="n">
-        <v>-3.254</v>
+        <v>-3.69</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.1947</v>
+        <v>-0.216</v>
       </c>
       <c r="J218" t="n">
-        <v>-3.894</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.74</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.264</v>
+        <v>-0.2841</v>
       </c>
       <c r="J219" t="n">
-        <v>-5.28</v>
+        <v>-5.682</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.65</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3464</v>
+        <v>-0.3642</v>
       </c>
       <c r="J220" t="n">
-        <v>-6.928</v>
+        <v>-7.284</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.58</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4118</v>
+        <v>-0.4266</v>
       </c>
       <c r="J221" t="n">
-        <v>-8.236000000000001</v>
+        <v>-8.532</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>2.18</v>
       </c>
       <c r="I222" t="n">
-        <v>1.8338</v>
+        <v>1.8701</v>
       </c>
       <c r="J222" t="n">
-        <v>36.676</v>
+        <v>37.402</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.61</v>
       </c>
       <c r="I223" t="n">
-        <v>1.2191</v>
+        <v>1.1987</v>
       </c>
       <c r="J223" t="n">
-        <v>24.382</v>
+        <v>23.974</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.37</v>
       </c>
       <c r="I224" t="n">
-        <v>0.888</v>
+        <v>0.8476</v>
       </c>
       <c r="J224" t="n">
-        <v>17.76</v>
+        <v>16.952</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.32</v>
       </c>
       <c r="I225" t="n">
-        <v>0.7776999999999999</v>
+        <v>0.7509</v>
       </c>
       <c r="J225" t="n">
-        <v>15.554</v>
+        <v>15.018</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.11</v>
       </c>
       <c r="I226" t="n">
-        <v>0.2605</v>
+        <v>0.2872</v>
       </c>
       <c r="J226" t="n">
-        <v>5.21</v>
+        <v>5.744</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.93</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.0359</v>
+        <v>-0.0615</v>
       </c>
       <c r="J227" t="n">
-        <v>-0.718</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.82</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1679</v>
+        <v>-0.193</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.358</v>
+        <v>-3.86</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.8</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1898</v>
+        <v>-0.2143</v>
       </c>
       <c r="J229" t="n">
-        <v>-3.796</v>
+        <v>-4.286</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.42</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.551</v>
+        <v>-0.5586</v>
       </c>
       <c r="J230" t="n">
-        <v>-11.02</v>
+        <v>-11.172</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.32</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6453</v>
+        <v>-0.6456</v>
       </c>
       <c r="J231" t="n">
-        <v>-12.906</v>
+        <v>-12.912</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2573/event_2573_evp_summary.xlsx
+++ b/database/event/2573/event_2573_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.0202</v>
+        <v>6.8957</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8482</v>
+        <v>0.8331</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5715</v>
+        <v>2.5355</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0202</v>
+        <v>6.8957</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6202</v>
+        <v>3.5742</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4</v>
+        <v>3.3215</v>
       </c>
       <c r="H2" t="n">
-        <v>7.0503</v>
+        <v>6.9763</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8071</v>
+        <v>3.917</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.3215</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
@@ -529,7 +529,7 @@
         <v>147</v>
       </c>
       <c r="M2" t="n">
-        <v>7.207100000000001</v>
+        <v>7.2385</v>
       </c>
       <c r="N2" t="n">
         <v>184</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8153</v>
+        <v>5.8955</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7026</v>
+        <v>0.7123</v>
       </c>
       <c r="D3" t="n">
-        <v>2.023</v>
+        <v>2.0799</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8153</v>
+        <v>5.8955</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5775</v>
+        <v>2.6479</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2378</v>
+        <v>3.2476</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6099</v>
+        <v>3.4987</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9493</v>
+        <v>1.9644</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2378</v>
+        <v>3.2476</v>
       </c>
       <c r="K3" t="n">
         <v>37</v>
@@ -575,7 +575,7 @@
         <v>147</v>
       </c>
       <c r="M3" t="n">
-        <v>5.1871</v>
+        <v>5.212</v>
       </c>
       <c r="N3" t="n">
         <v>184</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.3619</v>
+        <v>5.0719</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6478</v>
+        <v>0.6128</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8166</v>
+        <v>1.7047</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3619</v>
+        <v>5.0719</v>
       </c>
       <c r="F4" t="n">
-        <v>4.1133</v>
+        <v>3.9744</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2486</v>
+        <v>1.0975</v>
       </c>
       <c r="H4" t="n">
-        <v>8.677</v>
+        <v>8.4788</v>
       </c>
       <c r="I4" t="n">
-        <v>4.6855</v>
+        <v>4.7606</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2486</v>
+        <v>1.0975</v>
       </c>
       <c r="K4" t="n">
         <v>84</v>
@@ -621,7 +621,7 @@
         <v>96</v>
       </c>
       <c r="M4" t="n">
-        <v>5.9341</v>
+        <v>5.8581</v>
       </c>
       <c r="N4" t="n">
         <v>180</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.3734</v>
+        <v>4.3346</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5284</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3667</v>
+        <v>1.3688</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3734</v>
+        <v>4.3346</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9987</v>
+        <v>3.0212</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3747</v>
+        <v>1.3134</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9995</v>
+        <v>4.9004</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6997</v>
+        <v>2.7514</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3747</v>
+        <v>1.3134</v>
       </c>
       <c r="K5" t="n">
         <v>47</v>
@@ -667,7 +667,7 @@
         <v>108</v>
       </c>
       <c r="M5" t="n">
-        <v>4.0744</v>
+        <v>4.0648</v>
       </c>
       <c r="N5" t="n">
         <v>155</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2554</v>
+        <v>4.0435</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5141</v>
+        <v>0.4885</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3129</v>
+        <v>1.2362</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2554</v>
+        <v>4.0435</v>
       </c>
       <c r="F6" t="n">
-        <v>3.8432</v>
+        <v>3.7119</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4122</v>
+        <v>0.3316</v>
       </c>
       <c r="H6" t="n">
-        <v>7.7859</v>
+        <v>7.4936</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2043</v>
+        <v>4.2074</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4122</v>
+        <v>0.3316</v>
       </c>
       <c r="K6" t="n">
         <v>84</v>
@@ -713,7 +713,7 @@
         <v>96</v>
       </c>
       <c r="M6" t="n">
-        <v>4.6165</v>
+        <v>4.539</v>
       </c>
       <c r="N6" t="n">
         <v>180</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0633</v>
+        <v>3.8385</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4909</v>
+        <v>0.4638</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2255</v>
+        <v>1.1428</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0633</v>
+        <v>3.8385</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5211</v>
+        <v>1.3792</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5422</v>
+        <v>2.4593</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5211</v>
+        <v>1.3792</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8214</v>
+        <v>0.7744</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5422</v>
+        <v>2.4593</v>
       </c>
       <c r="K7" t="n">
         <v>37</v>
@@ -759,7 +759,7 @@
         <v>147</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3636</v>
+        <v>3.2337</v>
       </c>
       <c r="N7" t="n">
         <v>184</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0943</v>
+        <v>3.1887</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3739</v>
+        <v>0.3853</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7844</v>
+        <v>0.8468</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0943</v>
+        <v>3.1887</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3648</v>
+        <v>2.457</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7295</v>
+        <v>0.7317</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9082</v>
+        <v>2.782</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5704</v>
+        <v>1.562</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7295</v>
+        <v>0.7317</v>
       </c>
       <c r="K8" t="n">
         <v>37</v>
@@ -805,7 +805,7 @@
         <v>147</v>
       </c>
       <c r="M8" t="n">
-        <v>2.2999</v>
+        <v>2.2937</v>
       </c>
       <c r="N8" t="n">
         <v>184</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8685</v>
+        <v>2.8675</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3466</v>
+        <v>0.3464</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6816</v>
+        <v>0.7005</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8685</v>
+        <v>2.8675</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0364</v>
+        <v>3.0375</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1679</v>
+        <v>-0.17</v>
       </c>
       <c r="H9" t="n">
-        <v>5.1242</v>
+        <v>4.9616</v>
       </c>
       <c r="I9" t="n">
-        <v>2.767</v>
+        <v>2.7858</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1679</v>
+        <v>-0.17</v>
       </c>
       <c r="K9" t="n">
         <v>84</v>
@@ -851,7 +851,7 @@
         <v>96</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5991</v>
+        <v>2.6158</v>
       </c>
       <c r="N9" t="n">
         <v>180</v>
@@ -860,81 +860,81 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7972</v>
+        <v>2.7704</v>
       </c>
       <c r="C10" t="n">
-        <v>0.338</v>
+        <v>0.3347</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6491</v>
+        <v>0.6563</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7972</v>
+        <v>2.7704</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1219</v>
+        <v>2.932</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3247</v>
+        <v>-0.1616</v>
       </c>
       <c r="H10" t="n">
-        <v>5.406</v>
+        <v>4.5653</v>
       </c>
       <c r="I10" t="n">
-        <v>2.9192</v>
+        <v>2.5633</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3247</v>
+        <v>-0.1616</v>
       </c>
       <c r="K10" t="n">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="L10" t="n">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5945</v>
+        <v>2.4017</v>
       </c>
       <c r="N10" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7394</v>
+        <v>2.7479</v>
       </c>
       <c r="C11" t="n">
-        <v>0.331</v>
+        <v>0.332</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6228</v>
+        <v>0.646</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7394</v>
+        <v>2.7479</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4706</v>
+        <v>3.1091</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2688</v>
+        <v>-0.3612</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4706</v>
+        <v>5.2304</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7941</v>
+        <v>2.9367</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2688</v>
+        <v>-0.3612</v>
       </c>
       <c r="K11" t="n">
         <v>84</v>
@@ -943,7 +943,7 @@
         <v>96</v>
       </c>
       <c r="M11" t="n">
-        <v>2.0629</v>
+        <v>2.5755</v>
       </c>
       <c r="N11" t="n">
         <v>180</v>
@@ -952,139 +952,139 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.6312</v>
+        <v>2.587</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3179</v>
+        <v>0.3126</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5736</v>
+        <v>0.5727</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6312</v>
+        <v>2.587</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8962</v>
+        <v>1.4608</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.265</v>
+        <v>1.1262</v>
       </c>
       <c r="H12" t="n">
-        <v>4.6614</v>
+        <v>1.4608</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5171</v>
+        <v>0.8202</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.265</v>
+        <v>1.1262</v>
       </c>
       <c r="K12" t="n">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="L12" t="n">
-        <v>147</v>
+        <v>96</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2521</v>
+        <v>1.9464</v>
       </c>
       <c r="N12" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5413</v>
+        <v>2.5691</v>
       </c>
       <c r="C13" t="n">
-        <v>0.307</v>
+        <v>0.3104</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5326</v>
+        <v>0.5646</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5413</v>
+        <v>2.5691</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5413</v>
+        <v>2.4512</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.1179</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8371</v>
+        <v>2.7604</v>
       </c>
       <c r="I13" t="n">
-        <v>2.9102</v>
+        <v>1.5499</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.1179</v>
       </c>
       <c r="K13" t="n">
-        <v>190</v>
+        <v>129</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9102</v>
+        <v>1.6678</v>
       </c>
       <c r="N13" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5373</v>
+        <v>2.4579</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3066</v>
+        <v>0.297</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5308</v>
+        <v>0.5139</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5373</v>
+        <v>2.4579</v>
       </c>
       <c r="F14" t="n">
-        <v>2.39</v>
+        <v>2.4579</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1473</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9912</v>
+        <v>2.6827</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6152</v>
+        <v>2.7543</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1473</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>129</v>
+        <v>190</v>
       </c>
       <c r="L14" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7625</v>
+        <v>2.7543</v>
       </c>
       <c r="N14" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5202</v>
+        <v>2.3944</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3045</v>
+        <v>0.2893</v>
       </c>
       <c r="D15" t="n">
-        <v>0.523</v>
+        <v>0.485</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5202</v>
+        <v>2.3944</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1398</v>
+        <v>2.0204</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3804</v>
+        <v>0.374</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1658</v>
+        <v>2.0204</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1695</v>
+        <v>1.1344</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3804</v>
+        <v>0.374</v>
       </c>
       <c r="K15" t="n">
         <v>47</v>
@@ -1127,7 +1127,7 @@
         <v>108</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5499</v>
+        <v>1.5084</v>
       </c>
       <c r="N15" t="n">
         <v>155</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.445</v>
+        <v>2.3544</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2954</v>
+        <v>0.2845</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4888</v>
+        <v>0.4668</v>
       </c>
       <c r="E16" t="n">
-        <v>2.445</v>
+        <v>2.3544</v>
       </c>
       <c r="F16" t="n">
-        <v>2.445</v>
+        <v>2.3544</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6263</v>
+        <v>2.4454</v>
       </c>
       <c r="I16" t="n">
-        <v>2.694</v>
+        <v>2.5108</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.694</v>
+        <v>2.5108</v>
       </c>
       <c r="N16" t="n">
         <v>190</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2604</v>
+        <v>2.3496</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2731</v>
+        <v>0.2839</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4048</v>
+        <v>0.4646</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2604</v>
+        <v>2.3496</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5849</v>
+        <v>2.6388</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3245</v>
+        <v>-0.2892</v>
       </c>
       <c r="H17" t="n">
-        <v>3.6343</v>
+        <v>3.4645</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9625</v>
+        <v>1.9452</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3245</v>
+        <v>-0.2892</v>
       </c>
       <c r="K17" t="n">
         <v>129</v>
@@ -1219,7 +1219,7 @@
         <v>57</v>
       </c>
       <c r="M17" t="n">
-        <v>1.638</v>
+        <v>1.656</v>
       </c>
       <c r="N17" t="n">
         <v>186</v>
@@ -1228,35 +1228,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>gob b</t>
+          <t>keev</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.0873</v>
+        <v>2.1305</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2522</v>
+        <v>0.2574</v>
       </c>
       <c r="D18" t="n">
-        <v>0.326</v>
+        <v>0.3648</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0873</v>
+        <v>2.1305</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0511</v>
+        <v>2.4802</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0362</v>
+        <v>-0.3497</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0511</v>
+        <v>2.8693</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5676</v>
+        <v>1.611</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0362</v>
+        <v>-0.3497</v>
       </c>
       <c r="K18" t="n">
         <v>47</v>
@@ -1265,7 +1265,7 @@
         <v>108</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6038</v>
+        <v>1.2613</v>
       </c>
       <c r="N18" t="n">
         <v>155</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>keev</t>
+          <t>Nifty</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.0441</v>
+        <v>2.0033</v>
       </c>
       <c r="C19" t="n">
-        <v>0.247</v>
+        <v>0.242</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3063</v>
+        <v>0.3068</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0441</v>
+        <v>2.0033</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4021</v>
+        <v>1.5126</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.358</v>
+        <v>0.4907</v>
       </c>
       <c r="H19" t="n">
-        <v>3.0312</v>
+        <v>1.5126</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6368</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.358</v>
+        <v>0.4907</v>
       </c>
       <c r="K19" t="n">
-        <v>47</v>
+        <v>129</v>
       </c>
       <c r="L19" t="n">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2788</v>
+        <v>1.34</v>
       </c>
       <c r="N19" t="n">
-        <v>155</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nifty</t>
+          <t>gob b</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.0377</v>
+        <v>1.9908</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2462</v>
+        <v>0.2405</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3034</v>
+        <v>0.3011</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0377</v>
+        <v>1.9908</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5345</v>
+        <v>1.0442</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5032</v>
+        <v>0.9466</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5345</v>
+        <v>1.0442</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8286</v>
+        <v>0.5863</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5032</v>
+        <v>0.9466</v>
       </c>
       <c r="K20" t="n">
-        <v>129</v>
+        <v>47</v>
       </c>
       <c r="L20" t="n">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3318</v>
+        <v>1.5329</v>
       </c>
       <c r="N20" t="n">
-        <v>186</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0315</v>
+        <v>1.9025</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2454</v>
+        <v>0.2299</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3006</v>
+        <v>0.2609</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0315</v>
+        <v>1.9025</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0315</v>
+        <v>1.9025</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0315</v>
+        <v>1.9025</v>
       </c>
       <c r="I21" t="n">
-        <v>2.0839</v>
+        <v>1.9534</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.0839</v>
+        <v>1.9534</v>
       </c>
       <c r="N21" t="n">
         <v>190</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.9614</v>
+        <v>1.8065</v>
       </c>
       <c r="C22" t="n">
-        <v>0.237</v>
+        <v>0.2183</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2687</v>
+        <v>0.2172</v>
       </c>
       <c r="E22" t="n">
-        <v>1.9614</v>
+        <v>1.8065</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9614</v>
+        <v>1.8065</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9614</v>
+        <v>1.8065</v>
       </c>
       <c r="I22" t="n">
-        <v>2.0119</v>
+        <v>1.8548</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.0119</v>
+        <v>1.8548</v>
       </c>
       <c r="N22" t="n">
         <v>190</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.0288</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1243</v>
+        <v>0.1139</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1559</v>
+        <v>-0.1762</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0288</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0288</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0288</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0288</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0288</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="N23" t="n">
         <v>79</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3777</v>
+        <v>0.3605</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0456</v>
+        <v>0.0436</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4523</v>
+        <v>-0.4416</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3777</v>
+        <v>0.3605</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3777</v>
+        <v>0.3605</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3777</v>
+        <v>0.3605</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3777</v>
+        <v>0.3605</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3777</v>
+        <v>0.3605</v>
       </c>
       <c r="N24" t="n">
         <v>98</v>
@@ -1550,78 +1550,78 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FNS</t>
+          <t>Maniac</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3676</v>
+        <v>0.2736</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0444</v>
+        <v>0.0331</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4569</v>
+        <v>-0.4812</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3676</v>
+        <v>0.2736</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3676</v>
+        <v>0.2736</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3676</v>
+        <v>0.2736</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3771</v>
+        <v>0.2736</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>190</v>
+        <v>116</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3771</v>
+        <v>0.2736</v>
       </c>
       <c r="N25" t="n">
-        <v>190</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Maniac</t>
+          <t>Ex6TenZ</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3169</v>
+        <v>0.2639</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0383</v>
+        <v>0.0319</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4799</v>
+        <v>-0.4856</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3169</v>
+        <v>0.2639</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3169</v>
+        <v>0.2639</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3169</v>
+        <v>0.2639</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3169</v>
+        <v>0.2639</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3169</v>
+        <v>0.2639</v>
       </c>
       <c r="N26" t="n">
         <v>116</v>
@@ -1642,47 +1642,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ex6TenZ</t>
+          <t>FNS</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2909</v>
+        <v>0.2483</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0351</v>
+        <v>0.03</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4918</v>
+        <v>-0.4927</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2909</v>
+        <v>0.2483</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2909</v>
+        <v>0.2483</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2909</v>
+        <v>0.2483</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2909</v>
+        <v>0.255</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>116</v>
+        <v>190</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2909</v>
+        <v>0.255</v>
       </c>
       <c r="N27" t="n">
-        <v>116</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2219</v>
+        <v>0.1807</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0268</v>
+        <v>0.0218</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5232</v>
+        <v>-0.5235</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2219</v>
+        <v>0.1807</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2219</v>
+        <v>0.1807</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2219</v>
+        <v>0.1807</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2219</v>
+        <v>0.1807</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2219</v>
+        <v>0.1807</v>
       </c>
       <c r="N28" t="n">
         <v>98</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0476</v>
+        <v>-0.1009</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0058</v>
+        <v>-0.0122</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6459</v>
+        <v>-0.6518</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0476</v>
+        <v>-0.1009</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0476</v>
+        <v>-0.1009</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0476</v>
+        <v>-0.1009</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0476</v>
+        <v>-0.1009</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0476</v>
+        <v>-0.1009</v>
       </c>
       <c r="N29" t="n">
         <v>116</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2037</v>
+        <v>-0.2051</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0246</v>
+        <v>-0.0248</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7169</v>
+        <v>-0.6992</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2037</v>
+        <v>-0.2051</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2037</v>
+        <v>-0.2051</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2037</v>
+        <v>-0.2051</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2037</v>
+        <v>-0.2051</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2037</v>
+        <v>-0.2051</v>
       </c>
       <c r="N30" t="n">
         <v>79</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2348</v>
+        <v>-0.2461</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0284</v>
+        <v>-0.0297</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7311</v>
+        <v>-0.7179</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2348</v>
+        <v>-0.2461</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2348</v>
+        <v>-0.2461</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2348</v>
+        <v>-0.2461</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2348</v>
+        <v>-0.2461</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2348</v>
+        <v>-0.2461</v>
       </c>
       <c r="N31" t="n">
         <v>79</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.279</v>
+        <v>-0.3099</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0337</v>
+        <v>-0.0374</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7512</v>
+        <v>-0.747</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.279</v>
+        <v>-0.3099</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.279</v>
+        <v>-0.3099</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.279</v>
+        <v>-0.3099</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.279</v>
+        <v>-0.3099</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.279</v>
+        <v>-0.3099</v>
       </c>
       <c r="N32" t="n">
         <v>79</v>
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.419</v>
+        <v>-0.478</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0506</v>
+        <v>-0.0578</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8149</v>
+        <v>-0.8235</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.419</v>
+        <v>-0.478</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1594</v>
+        <v>-0.1441</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.2596</v>
+        <v>-0.3339</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1594</v>
+        <v>-0.1441</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0861</v>
+        <v>-0.0809</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.2596</v>
+        <v>-0.3339</v>
       </c>
       <c r="K33" t="n">
         <v>47</v>
@@ -1955,7 +1955,7 @@
         <v>108</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3457</v>
+        <v>-0.4147999999999999</v>
       </c>
       <c r="N33" t="n">
         <v>155</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4535</v>
+        <v>-0.4952</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0548</v>
+        <v>-0.0598</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8306</v>
+        <v>-0.8314</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4535</v>
+        <v>-0.4952</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4535</v>
+        <v>-0.4952</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4535</v>
+        <v>-0.4952</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4535</v>
+        <v>-0.4952</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4535</v>
+        <v>-0.4952</v>
       </c>
       <c r="N34" t="n">
         <v>116</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7462</v>
+        <v>-0.8849</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0902</v>
+        <v>-0.1069</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9639</v>
+        <v>-1.0089</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7462</v>
+        <v>-0.8849</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7462</v>
+        <v>-0.8849</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7462</v>
+        <v>-0.8849</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7462</v>
+        <v>-0.8849</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7462</v>
+        <v>-0.8849</v>
       </c>
       <c r="N35" t="n">
         <v>98</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.945</v>
+        <v>-0.9083</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1142</v>
+        <v>-0.1097</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0544</v>
+        <v>-1.0196</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.945</v>
+        <v>-0.9083</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.945</v>
+        <v>-0.9083</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.945</v>
+        <v>-0.9083</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.945</v>
+        <v>-0.9083</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.945</v>
+        <v>-0.9083</v>
       </c>
       <c r="N36" t="n">
         <v>98</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1618</v>
+        <v>-1.1254</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1404</v>
+        <v>-0.136</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1531</v>
+        <v>-1.1185</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1618</v>
+        <v>-1.1254</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.1618</v>
+        <v>-1.1254</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.1618</v>
+        <v>-1.1254</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1618</v>
+        <v>-1.1254</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1618</v>
+        <v>-1.1254</v>
       </c>
       <c r="N37" t="n">
         <v>79</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2354</v>
+        <v>-1.2025</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1493</v>
+        <v>-0.1453</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1866</v>
+        <v>-1.1536</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2354</v>
+        <v>-1.2025</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.3528</v>
+        <v>-1.2897</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1174</v>
+        <v>0.0872</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.3528</v>
+        <v>-1.2897</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.7305</v>
+        <v>-0.7241</v>
       </c>
       <c r="J38" t="n">
-        <v>0.1174</v>
+        <v>0.0872</v>
       </c>
       <c r="K38" t="n">
         <v>129</v>
@@ -2185,7 +2185,7 @@
         <v>57</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.6131</v>
+        <v>-0.6369</v>
       </c>
       <c r="N38" t="n">
         <v>186</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.4601</v>
+        <v>-1.4225</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1764</v>
+        <v>-0.1719</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2889</v>
+        <v>-1.2538</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4601</v>
+        <v>-1.4225</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4601</v>
+        <v>-1.4225</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.4601</v>
+        <v>-1.4225</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.4601</v>
+        <v>-1.4225</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.4601</v>
+        <v>-1.4225</v>
       </c>
       <c r="N39" t="n">
         <v>98</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.957</v>
+        <v>-1.8629</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2364</v>
+        <v>-0.2251</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5151</v>
+        <v>-1.4544</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.957</v>
+        <v>-1.8629</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.957</v>
+        <v>-1.8629</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.957</v>
+        <v>-1.8629</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.957</v>
+        <v>-1.8629</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.957</v>
+        <v>-1.8629</v>
       </c>
       <c r="N40" t="n">
         <v>116</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.8497</v>
+        <v>-2.6908</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3443</v>
+        <v>-0.3251</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.9214</v>
+        <v>-1.8316</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.8497</v>
+        <v>-2.6908</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.9623</v>
+        <v>-2.769</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1126</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.9623</v>
+        <v>-2.769</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.5996</v>
+        <v>-1.5547</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1126</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="K41" t="n">
         <v>129</v>
@@ -2323,7 +2323,7 @@
         <v>57</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.487</v>
+        <v>-1.4765</v>
       </c>
       <c r="N41" t="n">
         <v>186</v>
@@ -2429,10 +2429,10 @@
         <v>1.28</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5778</v>
+        <v>0.52</v>
       </c>
       <c r="J2" t="n">
-        <v>16.7562</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.19</v>
       </c>
       <c r="I3" t="n">
-        <v>0.427</v>
+        <v>0.3701</v>
       </c>
       <c r="J3" t="n">
-        <v>12.383</v>
+        <v>10.7329</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.11</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2805</v>
+        <v>0.2312</v>
       </c>
       <c r="J4" t="n">
-        <v>8.134499999999999</v>
+        <v>6.7048</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.61</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4249</v>
+        <v>-0.4168</v>
       </c>
       <c r="J5" t="n">
-        <v>-12.3221</v>
+        <v>-12.0872</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.6</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4337</v>
+        <v>-0.4265</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.5773</v>
+        <v>-12.3685</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.62</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3578</v>
+        <v>1.3923</v>
       </c>
       <c r="J7" t="n">
-        <v>39.3762</v>
+        <v>40.3767</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.3</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7526</v>
+        <v>0.7255</v>
       </c>
       <c r="J8" t="n">
-        <v>21.8254</v>
+        <v>21.0395</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4565</v>
+        <v>0.422</v>
       </c>
       <c r="J9" t="n">
-        <v>13.2385</v>
+        <v>12.238</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.02</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0673</v>
+        <v>0.0511</v>
       </c>
       <c r="J10" t="n">
-        <v>1.9517</v>
+        <v>1.4819</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.91</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3535</v>
+        <v>-0.3128</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.2515</v>
+        <v>-9.071199999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.89</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1235</v>
+        <v>-0.1075</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.717</v>
+        <v>-2.365</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.83</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1913</v>
+        <v>-0.1758</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.2086</v>
+        <v>-3.8676</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.77</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2529</v>
+        <v>-0.2384</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.5638</v>
+        <v>-5.2448</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.62</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3883</v>
+        <v>-0.3767</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.5426</v>
+        <v>-8.2874</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.4</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5813</v>
+        <v>-0.591</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.7886</v>
+        <v>-13.002</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.69</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4127</v>
+        <v>1.4496</v>
       </c>
       <c r="J17" t="n">
-        <v>31.0794</v>
+        <v>31.8912</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.5</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0885</v>
+        <v>1.0977</v>
       </c>
       <c r="J18" t="n">
-        <v>23.947</v>
+        <v>24.1494</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.46</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0188</v>
+        <v>1.022</v>
       </c>
       <c r="J19" t="n">
-        <v>22.4136</v>
+        <v>22.484</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.45</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0014</v>
+        <v>1.0032</v>
       </c>
       <c r="J20" t="n">
-        <v>22.0308</v>
+        <v>22.0704</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.14</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3717</v>
+        <v>0.3394</v>
       </c>
       <c r="J21" t="n">
-        <v>8.1774</v>
+        <v>7.4668</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.5</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9784</v>
+        <v>0.9663</v>
       </c>
       <c r="J22" t="n">
-        <v>29.352</v>
+        <v>28.989</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.15</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4405</v>
+        <v>0.4049</v>
       </c>
       <c r="J23" t="n">
-        <v>13.215</v>
+        <v>12.147</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.15</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4405</v>
+        <v>0.4049</v>
       </c>
       <c r="J24" t="n">
-        <v>13.215</v>
+        <v>12.147</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.96</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1893</v>
+        <v>-0.1548</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.679</v>
+        <v>-4.644</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.8</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6098</v>
+        <v>-0.573</v>
       </c>
       <c r="J26" t="n">
-        <v>-18.294</v>
+        <v>-17.19</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.21</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4426</v>
+        <v>0.3885</v>
       </c>
       <c r="J27" t="n">
-        <v>13.278</v>
+        <v>11.655</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.19</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4121</v>
+        <v>0.3558</v>
       </c>
       <c r="J28" t="n">
-        <v>12.363</v>
+        <v>10.674</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.11</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2687</v>
+        <v>0.221</v>
       </c>
       <c r="J29" t="n">
-        <v>8.061</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.84</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2135</v>
+        <v>-0.1929</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.405</v>
+        <v>-5.787</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.74</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.312</v>
+        <v>-0.2949</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.359999999999999</v>
+        <v>-8.847</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.2</v>
       </c>
       <c r="I32" t="n">
-        <v>0.367</v>
+        <v>0.3638</v>
       </c>
       <c r="J32" t="n">
-        <v>9.542</v>
+        <v>9.4588</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0151</v>
+        <v>0.0124</v>
       </c>
       <c r="J33" t="n">
-        <v>0.3926</v>
+        <v>0.3224</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.91</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1268</v>
+        <v>-0.1106</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.2968</v>
+        <v>-2.8756</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.67</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3637</v>
+        <v>-0.3494</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.456200000000001</v>
+        <v>-9.0844</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.62</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4087</v>
+        <v>-0.3982</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.6262</v>
+        <v>-10.3532</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.37</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4729</v>
+        <v>0.4184</v>
       </c>
       <c r="J37" t="n">
-        <v>12.2954</v>
+        <v>10.8784</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.24</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3431</v>
+        <v>0.2871</v>
       </c>
       <c r="J38" t="n">
-        <v>8.9206</v>
+        <v>7.4646</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.22</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3205</v>
+        <v>0.2667</v>
       </c>
       <c r="J39" t="n">
-        <v>8.333</v>
+        <v>6.9342</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.21</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3089</v>
+        <v>0.2563</v>
       </c>
       <c r="J40" t="n">
-        <v>8.0314</v>
+        <v>6.6638</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.14</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2219</v>
+        <v>0.1791</v>
       </c>
       <c r="J41" t="n">
-        <v>5.7694</v>
+        <v>4.6566</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.46</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9062</v>
+        <v>0.8912</v>
       </c>
       <c r="J42" t="n">
-        <v>36.248</v>
+        <v>35.648</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.4</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.8053</v>
       </c>
       <c r="J43" t="n">
-        <v>32.844</v>
+        <v>32.212</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.27</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6287</v>
+        <v>0.6168</v>
       </c>
       <c r="J44" t="n">
-        <v>25.148</v>
+        <v>24.672</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0297</v>
+        <v>-0.0241</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.188</v>
+        <v>-0.964</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.76</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7118</v>
+        <v>-0.6832</v>
       </c>
       <c r="J46" t="n">
-        <v>-28.472</v>
+        <v>-27.328</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.25</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5057</v>
+        <v>0.471</v>
       </c>
       <c r="J47" t="n">
-        <v>20.228</v>
+        <v>18.84</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.24</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4934</v>
+        <v>0.4546</v>
       </c>
       <c r="J48" t="n">
-        <v>19.736</v>
+        <v>18.184</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.88</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1654</v>
+        <v>-0.1457</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.616</v>
+        <v>-5.828</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.87</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1763</v>
+        <v>-0.1562</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.052</v>
+        <v>-6.248</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.54</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4856</v>
+        <v>-0.4847</v>
       </c>
       <c r="J51" t="n">
-        <v>-19.424</v>
+        <v>-19.388</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.36</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7565</v>
+        <v>0.7418</v>
       </c>
       <c r="J52" t="n">
-        <v>20.4255</v>
+        <v>20.0286</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.29</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6419</v>
       </c>
       <c r="J53" t="n">
-        <v>17.6499</v>
+        <v>17.3313</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.2</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5162</v>
+        <v>0.5071</v>
       </c>
       <c r="J54" t="n">
-        <v>13.9374</v>
+        <v>13.6917</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.13</v>
       </c>
       <c r="I55" t="n">
-        <v>0.383</v>
+        <v>0.3494</v>
       </c>
       <c r="J55" t="n">
-        <v>10.341</v>
+        <v>9.4338</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.11</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3331</v>
+        <v>0.3002</v>
       </c>
       <c r="J56" t="n">
-        <v>8.9937</v>
+        <v>8.105399999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.12</v>
       </c>
       <c r="I57" t="n">
-        <v>0.303</v>
+        <v>0.2522</v>
       </c>
       <c r="J57" t="n">
-        <v>8.180999999999999</v>
+        <v>6.8094</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.1</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2639</v>
+        <v>0.2161</v>
       </c>
       <c r="J58" t="n">
-        <v>7.1253</v>
+        <v>5.8347</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.91</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1309</v>
+        <v>-0.1128</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.5343</v>
+        <v>-3.0456</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.8</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2472</v>
+        <v>-0.2272</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.6744</v>
+        <v>-6.1344</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.79</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2571</v>
+        <v>-0.2373</v>
       </c>
       <c r="J61" t="n">
-        <v>-6.9417</v>
+        <v>-6.4071</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.21</v>
       </c>
       <c r="I62" t="n">
-        <v>0.555</v>
+        <v>0.5437</v>
       </c>
       <c r="J62" t="n">
-        <v>16.65</v>
+        <v>16.311</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.11</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3574</v>
+        <v>0.3167</v>
       </c>
       <c r="J63" t="n">
-        <v>10.722</v>
+        <v>9.500999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.05</v>
       </c>
       <c r="I64" t="n">
-        <v>0.193</v>
+        <v>0.1614</v>
       </c>
       <c r="J64" t="n">
-        <v>5.79</v>
+        <v>4.842</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.99</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.0476</v>
       </c>
       <c r="J65" t="n">
-        <v>-1.983</v>
+        <v>-1.428</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.88</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4037</v>
+        <v>-0.3606</v>
       </c>
       <c r="J66" t="n">
-        <v>-12.111</v>
+        <v>-10.818</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.38</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6341</v>
+        <v>0.6035</v>
       </c>
       <c r="J67" t="n">
-        <v>19.023</v>
+        <v>18.105</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.17</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3697</v>
+        <v>0.3155</v>
       </c>
       <c r="J68" t="n">
-        <v>11.091</v>
+        <v>9.465</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.96</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.062</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.319</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.93</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1166</v>
+        <v>-0.0982</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.498</v>
+        <v>-2.946</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.87</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1856</v>
+        <v>-0.165</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.568</v>
+        <v>-4.95</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.83</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4498</v>
+        <v>1.4808</v>
       </c>
       <c r="J72" t="n">
-        <v>26.0964</v>
+        <v>26.6544</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.73</v>
       </c>
       <c r="I73" t="n">
-        <v>1.3325</v>
+        <v>1.3588</v>
       </c>
       <c r="J73" t="n">
-        <v>23.985</v>
+        <v>24.4584</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.71</v>
       </c>
       <c r="I74" t="n">
-        <v>1.3089</v>
+        <v>1.3345</v>
       </c>
       <c r="J74" t="n">
-        <v>23.5602</v>
+        <v>24.021</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.57</v>
       </c>
       <c r="I75" t="n">
-        <v>1.1416</v>
+        <v>1.1641</v>
       </c>
       <c r="J75" t="n">
-        <v>20.5488</v>
+        <v>20.9538</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.33</v>
       </c>
       <c r="I76" t="n">
-        <v>0.7551</v>
+        <v>0.742</v>
       </c>
       <c r="J76" t="n">
-        <v>13.5918</v>
+        <v>13.356</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.42</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.5134</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="J77" t="n">
-        <v>-9.241199999999999</v>
+        <v>-9.3726</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.4</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.5313</v>
+        <v>-0.5392</v>
       </c>
       <c r="J78" t="n">
-        <v>-9.5634</v>
+        <v>-9.7056</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.37</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.5642</v>
       </c>
       <c r="J79" t="n">
-        <v>-10.0062</v>
+        <v>-10.1556</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.37</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.5642</v>
       </c>
       <c r="J80" t="n">
-        <v>-10.0062</v>
+        <v>-10.1556</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.36</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5645</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.161</v>
+        <v>-10.3158</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>2.2</v>
       </c>
       <c r="I82" t="n">
-        <v>1.8963</v>
+        <v>1.9648</v>
       </c>
       <c r="J82" t="n">
-        <v>37.926</v>
+        <v>39.296</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.47</v>
       </c>
       <c r="I83" t="n">
-        <v>1.0214</v>
+        <v>1.0323</v>
       </c>
       <c r="J83" t="n">
-        <v>20.428</v>
+        <v>20.646</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.3</v>
       </c>
       <c r="I84" t="n">
-        <v>0.7133</v>
+        <v>0.6959</v>
       </c>
       <c r="J84" t="n">
-        <v>14.266</v>
+        <v>13.918</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.3</v>
       </c>
       <c r="I85" t="n">
-        <v>0.7133</v>
+        <v>0.6959</v>
       </c>
       <c r="J85" t="n">
-        <v>14.266</v>
+        <v>13.918</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.24</v>
       </c>
       <c r="I86" t="n">
-        <v>0.5896</v>
+        <v>0.5648</v>
       </c>
       <c r="J86" t="n">
-        <v>11.792</v>
+        <v>11.296</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.88</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.1345</v>
+        <v>-0.1183</v>
       </c>
       <c r="J87" t="n">
-        <v>-2.69</v>
+        <v>-2.366</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.78</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2423</v>
+        <v>-0.2278</v>
       </c>
       <c r="J88" t="n">
-        <v>-4.846</v>
+        <v>-4.556</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.73</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2905</v>
+        <v>-0.2767</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.81</v>
+        <v>-5.534</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.68</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3346</v>
+        <v>-0.3213</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.692</v>
+        <v>-6.426</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.42</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5635</v>
+        <v>-0.5704</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.27</v>
+        <v>-11.408</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.47</v>
       </c>
       <c r="I92" t="n">
-        <v>1.0812</v>
+        <v>1.0913</v>
       </c>
       <c r="J92" t="n">
-        <v>31.3548</v>
+        <v>31.6477</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.16</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4661</v>
+        <v>0.4272</v>
       </c>
       <c r="J93" t="n">
-        <v>13.5169</v>
+        <v>12.3888</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.08</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2695</v>
+        <v>0.2359</v>
       </c>
       <c r="J94" t="n">
-        <v>7.8155</v>
+        <v>6.8411</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.95</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2227</v>
+        <v>-0.1857</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.4583</v>
+        <v>-5.3853</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2532</v>
+        <v>-0.2143</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.3428</v>
+        <v>-6.2147</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.22</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4632</v>
+        <v>0.4048</v>
       </c>
       <c r="J97" t="n">
-        <v>13.4328</v>
+        <v>11.7392</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.21</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4465</v>
+        <v>0.3885</v>
       </c>
       <c r="J98" t="n">
-        <v>12.9485</v>
+        <v>11.2665</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.08</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2096</v>
+        <v>0.1679</v>
       </c>
       <c r="J99" t="n">
-        <v>6.0784</v>
+        <v>4.8691</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.8</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.254</v>
+        <v>-0.2343</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.366</v>
+        <v>-6.7947</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.78</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2737</v>
+        <v>-0.2546</v>
       </c>
       <c r="J101" t="n">
-        <v>-7.9373</v>
+        <v>-7.3834</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.26</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4194</v>
+        <v>0.4189</v>
       </c>
       <c r="J102" t="n">
-        <v>10.9044</v>
+        <v>10.8914</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.17</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3004</v>
+        <v>0.2883</v>
       </c>
       <c r="J103" t="n">
-        <v>7.8104</v>
+        <v>7.4958</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.91</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1347</v>
+        <v>-0.1157</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.5022</v>
+        <v>-3.0082</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.85</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2008</v>
+        <v>-0.1801</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.2208</v>
+        <v>-4.6826</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.77</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.281</v>
+        <v>-0.2622</v>
       </c>
       <c r="J106" t="n">
-        <v>-7.306</v>
+        <v>-6.8172</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.29</v>
       </c>
       <c r="I107" t="n">
-        <v>0.405</v>
+        <v>0.3422</v>
       </c>
       <c r="J107" t="n">
-        <v>10.53</v>
+        <v>8.8972</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.23</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3362</v>
+        <v>0.2792</v>
       </c>
       <c r="J108" t="n">
-        <v>8.741199999999999</v>
+        <v>7.2592</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.15</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2399</v>
+        <v>0.1937</v>
       </c>
       <c r="J109" t="n">
-        <v>6.2374</v>
+        <v>5.0362</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.12</v>
       </c>
       <c r="I110" t="n">
-        <v>0.2005</v>
+        <v>0.1595</v>
       </c>
       <c r="J110" t="n">
-        <v>5.213</v>
+        <v>4.147</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.07</v>
       </c>
       <c r="I111" t="n">
-        <v>0.128</v>
+        <v>0.098</v>
       </c>
       <c r="J111" t="n">
-        <v>3.328</v>
+        <v>2.548</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.46</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0657</v>
+        <v>1.0738</v>
       </c>
       <c r="J112" t="n">
-        <v>28.7739</v>
+        <v>28.9926</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.06</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2124</v>
+        <v>0.1824</v>
       </c>
       <c r="J113" t="n">
-        <v>5.7348</v>
+        <v>4.9248</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.05</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1824</v>
+        <v>0.1546</v>
       </c>
       <c r="J114" t="n">
-        <v>4.9248</v>
+        <v>4.1742</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.03</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1174</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="J115" t="n">
-        <v>3.1698</v>
+        <v>2.5839</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.02</v>
       </c>
       <c r="I116" t="n">
-        <v>0.081</v>
+        <v>0.0639</v>
       </c>
       <c r="J116" t="n">
-        <v>2.187</v>
+        <v>1.7253</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.33</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6312</v>
+        <v>0.5719</v>
       </c>
       <c r="J117" t="n">
-        <v>17.0424</v>
+        <v>15.4413</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.07</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1851</v>
+        <v>0.1474</v>
       </c>
       <c r="J118" t="n">
-        <v>4.9977</v>
+        <v>3.9798</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.06</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1641</v>
+        <v>0.1292</v>
       </c>
       <c r="J119" t="n">
-        <v>4.4307</v>
+        <v>3.4884</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.06</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1641</v>
+        <v>0.1292</v>
       </c>
       <c r="J120" t="n">
-        <v>4.4307</v>
+        <v>3.4884</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.72</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3333</v>
+        <v>-0.3179</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.9991</v>
+        <v>-8.583299999999999</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.22</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5969</v>
+        <v>0.5608</v>
       </c>
       <c r="J122" t="n">
-        <v>17.907</v>
+        <v>16.824</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.19</v>
       </c>
       <c r="I123" t="n">
-        <v>0.531</v>
+        <v>0.4934</v>
       </c>
       <c r="J123" t="n">
-        <v>15.93</v>
+        <v>14.802</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.18</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.4708</v>
       </c>
       <c r="J124" t="n">
-        <v>15.258</v>
+        <v>14.124</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.18</v>
       </c>
       <c r="I125" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.4708</v>
       </c>
       <c r="J125" t="n">
-        <v>15.258</v>
+        <v>14.124</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.93</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2863</v>
+        <v>-0.2461</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.589</v>
+        <v>-7.383</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.21</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4696</v>
+        <v>0.4126</v>
       </c>
       <c r="J127" t="n">
-        <v>14.088</v>
+        <v>12.378</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.16</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3812</v>
+        <v>0.3264</v>
       </c>
       <c r="J128" t="n">
-        <v>11.436</v>
+        <v>9.792</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.8</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2459</v>
+        <v>-0.2259</v>
       </c>
       <c r="J129" t="n">
-        <v>-7.377</v>
+        <v>-6.777</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.79</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2557</v>
+        <v>-0.236</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.671</v>
+        <v>-7.08</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3504</v>
+        <v>-0.3353</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.512</v>
+        <v>-10.059</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.42</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9933</v>
+        <v>0.9888</v>
       </c>
       <c r="J132" t="n">
-        <v>27.8124</v>
+        <v>27.6864</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.29</v>
       </c>
       <c r="I133" t="n">
-        <v>0.7403</v>
+        <v>0.711</v>
       </c>
       <c r="J133" t="n">
-        <v>20.7284</v>
+        <v>19.908</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.28</v>
       </c>
       <c r="I134" t="n">
-        <v>0.7197</v>
+        <v>0.6893</v>
       </c>
       <c r="J134" t="n">
-        <v>20.1516</v>
+        <v>19.3004</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.04</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1444</v>
+        <v>0.1202</v>
       </c>
       <c r="J135" t="n">
-        <v>4.0432</v>
+        <v>3.3656</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.78</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6644</v>
+        <v>-0.632</v>
       </c>
       <c r="J136" t="n">
-        <v>-18.6032</v>
+        <v>-17.696</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.5</v>
       </c>
       <c r="I137" t="n">
-        <v>0.9164</v>
+        <v>0.8773</v>
       </c>
       <c r="J137" t="n">
-        <v>25.6592</v>
+        <v>24.5644</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.1</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2617</v>
+        <v>0.214</v>
       </c>
       <c r="J138" t="n">
-        <v>7.3276</v>
+        <v>5.992</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.82</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2281</v>
+        <v>-0.2078</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.3868</v>
+        <v>-5.8184</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3527</v>
+        <v>-0.3379</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.8756</v>
+        <v>-9.4612</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.66</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3799</v>
+        <v>-0.3674</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.6372</v>
+        <v>-10.2872</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.1</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2692</v>
+        <v>0.2212</v>
       </c>
       <c r="J142" t="n">
-        <v>7.8068</v>
+        <v>6.4148</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.99</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.0196</v>
+        <v>-0.0145</v>
       </c>
       <c r="J143" t="n">
-        <v>-0.5684</v>
+        <v>-0.4205</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.91</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1294</v>
+        <v>-0.1119</v>
       </c>
       <c r="J144" t="n">
-        <v>-3.7526</v>
+        <v>-3.2451</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.89</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1517</v>
+        <v>-0.133</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.3993</v>
+        <v>-3.857</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.72</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3218</v>
+        <v>-0.3049</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.3322</v>
+        <v>-8.8421</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.33</v>
       </c>
       <c r="I147" t="n">
-        <v>0.8198</v>
+        <v>0.7958</v>
       </c>
       <c r="J147" t="n">
-        <v>23.7742</v>
+        <v>23.0782</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.24</v>
       </c>
       <c r="I148" t="n">
-        <v>0.6344</v>
+        <v>0.6007</v>
       </c>
       <c r="J148" t="n">
-        <v>18.3976</v>
+        <v>17.4203</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.19</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5266</v>
+        <v>0.4906</v>
       </c>
       <c r="J149" t="n">
-        <v>15.2714</v>
+        <v>14.2274</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.05</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1746</v>
+        <v>0.148</v>
       </c>
       <c r="J150" t="n">
-        <v>5.0634</v>
+        <v>4.292</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.04</v>
       </c>
       <c r="I151" t="n">
-        <v>0.143</v>
+        <v>0.119</v>
       </c>
       <c r="J151" t="n">
-        <v>4.147</v>
+        <v>3.451</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.46</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5987</v>
+        <v>0.5279</v>
       </c>
       <c r="J152" t="n">
-        <v>17.3623</v>
+        <v>15.3091</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.17</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2689</v>
+        <v>0.2177</v>
       </c>
       <c r="J153" t="n">
-        <v>7.7981</v>
+        <v>6.3133</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.13</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2174</v>
+        <v>0.1727</v>
       </c>
       <c r="J154" t="n">
-        <v>6.3046</v>
+        <v>5.0083</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.92</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1331</v>
+        <v>-0.1139</v>
       </c>
       <c r="J155" t="n">
-        <v>-3.8599</v>
+        <v>-3.3031</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.89</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.1679</v>
+        <v>-0.1477</v>
       </c>
       <c r="J156" t="n">
-        <v>-4.8691</v>
+        <v>-4.2833</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.08</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1666</v>
+        <v>0.1497</v>
       </c>
       <c r="J157" t="n">
-        <v>4.8314</v>
+        <v>4.3413</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.08</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1666</v>
+        <v>0.1497</v>
       </c>
       <c r="J158" t="n">
-        <v>4.8314</v>
+        <v>4.3413</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.03</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0785</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="J159" t="n">
-        <v>2.2765</v>
+        <v>1.8879</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.99</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.0251</v>
+        <v>-0.0181</v>
       </c>
       <c r="J160" t="n">
-        <v>-0.7279</v>
+        <v>-0.5249</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2423</v>
+        <v>-0.2221</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.0267</v>
+        <v>-6.4409</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.08</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3269</v>
+        <v>0.2996</v>
       </c>
       <c r="J162" t="n">
-        <v>6.538</v>
+        <v>5.992</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0078</v>
+        <v>0.0116</v>
       </c>
       <c r="J163" t="n">
-        <v>-0.156</v>
+        <v>0.232</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.55</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.4466</v>
+        <v>-0.4394</v>
       </c>
       <c r="J164" t="n">
-        <v>-8.932</v>
+        <v>-8.788</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.44</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.5432</v>
+        <v>-0.5468</v>
       </c>
       <c r="J165" t="n">
-        <v>-10.864</v>
+        <v>-10.936</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.33</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6387</v>
+        <v>-0.6579</v>
       </c>
       <c r="J166" t="n">
-        <v>-12.774</v>
+        <v>-13.158</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.68</v>
       </c>
       <c r="I167" t="n">
-        <v>1.3006</v>
+        <v>1.3205</v>
       </c>
       <c r="J167" t="n">
-        <v>26.012</v>
+        <v>26.41</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.57</v>
       </c>
       <c r="I168" t="n">
-        <v>1.1612</v>
+        <v>1.1769</v>
       </c>
       <c r="J168" t="n">
-        <v>23.224</v>
+        <v>23.538</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.47</v>
       </c>
       <c r="I169" t="n">
-        <v>1.0287</v>
+        <v>1.0365</v>
       </c>
       <c r="J169" t="n">
-        <v>20.574</v>
+        <v>20.73</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.37</v>
       </c>
       <c r="I170" t="n">
-        <v>0.8613</v>
+        <v>0.8507</v>
       </c>
       <c r="J170" t="n">
-        <v>17.226</v>
+        <v>17.014</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.95</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2706</v>
+        <v>-0.2389</v>
       </c>
       <c r="J171" t="n">
-        <v>-5.412</v>
+        <v>-4.778</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.45</v>
       </c>
       <c r="I172" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.7864</v>
       </c>
       <c r="J172" t="n">
-        <v>21.6892</v>
+        <v>20.4464</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.07</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1957</v>
+        <v>0.1549</v>
       </c>
       <c r="J173" t="n">
-        <v>5.0882</v>
+        <v>4.0274</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.97</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0567</v>
+        <v>-0.0449</v>
       </c>
       <c r="J174" t="n">
-        <v>-1.4742</v>
+        <v>-1.1674</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1672</v>
+        <v>-0.1471</v>
       </c>
       <c r="J175" t="n">
-        <v>-4.3472</v>
+        <v>-3.8246</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.51</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5127</v>
+        <v>-0.5158</v>
       </c>
       <c r="J176" t="n">
-        <v>-13.3302</v>
+        <v>-13.4108</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.74</v>
       </c>
       <c r="I177" t="n">
-        <v>1.4392</v>
+        <v>1.4723</v>
       </c>
       <c r="J177" t="n">
-        <v>37.4192</v>
+        <v>38.2798</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.22</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5955</v>
+        <v>0.5596</v>
       </c>
       <c r="J178" t="n">
-        <v>15.483</v>
+        <v>14.5496</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.07</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2373</v>
+        <v>0.2064</v>
       </c>
       <c r="J179" t="n">
-        <v>6.1698</v>
+        <v>5.3664</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.96</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.196</v>
+        <v>-0.1613</v>
       </c>
       <c r="J180" t="n">
-        <v>-5.096</v>
+        <v>-4.1938</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.75</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.7287</v>
+        <v>-0.7007</v>
       </c>
       <c r="J181" t="n">
-        <v>-18.9462</v>
+        <v>-18.2182</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>2.32</v>
       </c>
       <c r="I182" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J182" t="n">
-        <v>32.9324</v>
+        <v>33.6906</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.72</v>
       </c>
       <c r="I183" t="n">
-        <v>1.3184</v>
+        <v>1.3451</v>
       </c>
       <c r="J183" t="n">
-        <v>22.4128</v>
+        <v>22.8667</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.69</v>
       </c>
       <c r="I184" t="n">
-        <v>1.2832</v>
+        <v>1.309</v>
       </c>
       <c r="J184" t="n">
-        <v>21.8144</v>
+        <v>22.253</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.54</v>
       </c>
       <c r="I185" t="n">
-        <v>1.1017</v>
+        <v>1.1243</v>
       </c>
       <c r="J185" t="n">
-        <v>18.7289</v>
+        <v>19.1131</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.04</v>
       </c>
       <c r="I186" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0381</v>
       </c>
       <c r="J186" t="n">
-        <v>1.1985</v>
+        <v>0.6477000000000001</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.79</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1586</v>
+        <v>-0.1246</v>
       </c>
       <c r="J187" t="n">
-        <v>-2.6962</v>
+        <v>-2.1182</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2727</v>
+        <v>-0.255</v>
       </c>
       <c r="J188" t="n">
-        <v>-4.6359</v>
+        <v>-4.335</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.38</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.5643</v>
+        <v>-0.5703</v>
       </c>
       <c r="J189" t="n">
-        <v>-9.5931</v>
+        <v>-9.6951</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.25</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.6838</v>
+        <v>-0.7081</v>
       </c>
       <c r="J190" t="n">
-        <v>-11.6246</v>
+        <v>-12.0377</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.24</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6931</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.7827</v>
+        <v>-12.2281</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.65</v>
       </c>
       <c r="I192" t="n">
-        <v>1.2605</v>
+        <v>1.2791</v>
       </c>
       <c r="J192" t="n">
-        <v>26.4705</v>
+        <v>26.8611</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.48</v>
       </c>
       <c r="I193" t="n">
-        <v>1.0413</v>
+        <v>1.0514</v>
       </c>
       <c r="J193" t="n">
-        <v>21.8673</v>
+        <v>22.0794</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.41</v>
       </c>
       <c r="I194" t="n">
-        <v>0.9322</v>
+        <v>0.928</v>
       </c>
       <c r="J194" t="n">
-        <v>19.5762</v>
+        <v>19.488</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.32</v>
       </c>
       <c r="I195" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.7476</v>
       </c>
       <c r="J195" t="n">
-        <v>16.0356</v>
+        <v>15.6996</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.26</v>
       </c>
       <c r="I196" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.6198</v>
       </c>
       <c r="J196" t="n">
-        <v>13.4946</v>
+        <v>13.0158</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.08</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2801</v>
+        <v>0.2404</v>
       </c>
       <c r="J197" t="n">
-        <v>5.8821</v>
+        <v>5.0484</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.78</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.2506</v>
+        <v>-0.2342</v>
       </c>
       <c r="J198" t="n">
-        <v>-5.2626</v>
+        <v>-4.9182</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.76</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2688</v>
+        <v>-0.2524</v>
       </c>
       <c r="J199" t="n">
-        <v>-5.6448</v>
+        <v>-5.3004</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.62</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3959</v>
+        <v>-0.3841</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.3139</v>
+        <v>-8.0661</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.58</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4315</v>
+        <v>-0.4227</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.061500000000001</v>
+        <v>-8.8767</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.35</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6586</v>
+        <v>0.5996</v>
       </c>
       <c r="J202" t="n">
-        <v>19.758</v>
+        <v>17.988</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.14</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3173</v>
+        <v>0.2665</v>
       </c>
       <c r="J203" t="n">
-        <v>9.519</v>
+        <v>7.995</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.13</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2992</v>
+        <v>0.2499</v>
       </c>
       <c r="J204" t="n">
-        <v>8.976000000000001</v>
+        <v>7.497</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.85</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2068</v>
+        <v>-0.1862</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.204</v>
+        <v>-5.586</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.83</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2275</v>
+        <v>-0.2072</v>
       </c>
       <c r="J206" t="n">
-        <v>-6.825</v>
+        <v>-6.216</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.46</v>
       </c>
       <c r="I207" t="n">
-        <v>1.0642</v>
+        <v>1.072</v>
       </c>
       <c r="J207" t="n">
-        <v>31.926</v>
+        <v>32.16</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.35</v>
       </c>
       <c r="I208" t="n">
-        <v>0.8702</v>
+        <v>0.8494</v>
       </c>
       <c r="J208" t="n">
-        <v>26.106</v>
+        <v>25.482</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.27</v>
       </c>
       <c r="I209" t="n">
-        <v>0.7059</v>
+        <v>0.6738</v>
       </c>
       <c r="J209" t="n">
-        <v>21.177</v>
+        <v>20.214</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.79</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.636</v>
+        <v>-0.6011</v>
       </c>
       <c r="J210" t="n">
-        <v>-19.08</v>
+        <v>-18.033</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.78</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6587</v>
+        <v>-0.6252</v>
       </c>
       <c r="J211" t="n">
-        <v>-19.761</v>
+        <v>-18.756</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.82</v>
       </c>
       <c r="I212" t="n">
-        <v>1.4658</v>
+        <v>1.495</v>
       </c>
       <c r="J212" t="n">
-        <v>29.316</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.61</v>
       </c>
       <c r="I213" t="n">
-        <v>1.2071</v>
+        <v>1.2246</v>
       </c>
       <c r="J213" t="n">
-        <v>24.142</v>
+        <v>24.492</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.56</v>
       </c>
       <c r="I214" t="n">
-        <v>1.1437</v>
+        <v>1.1601</v>
       </c>
       <c r="J214" t="n">
-        <v>22.874</v>
+        <v>23.202</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.41</v>
       </c>
       <c r="I215" t="n">
-        <v>0.9301</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="J215" t="n">
-        <v>18.602</v>
+        <v>18.538</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.83</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5917</v>
+        <v>-0.5633</v>
       </c>
       <c r="J216" t="n">
-        <v>-11.834</v>
+        <v>-11.266</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.84</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.1845</v>
+        <v>-0.1689</v>
       </c>
       <c r="J217" t="n">
-        <v>-3.69</v>
+        <v>-3.378</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.216</v>
+        <v>-0.2007</v>
       </c>
       <c r="J218" t="n">
-        <v>-4.32</v>
+        <v>-4.014</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.74</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2841</v>
+        <v>-0.2692</v>
       </c>
       <c r="J219" t="n">
-        <v>-5.682</v>
+        <v>-5.384</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.65</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3642</v>
+        <v>-0.351</v>
       </c>
       <c r="J220" t="n">
-        <v>-7.284</v>
+        <v>-7.02</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.58</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4266</v>
+        <v>-0.4174</v>
       </c>
       <c r="J221" t="n">
-        <v>-8.532</v>
+        <v>-8.348000000000001</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>2.18</v>
       </c>
       <c r="I222" t="n">
-        <v>1.8701</v>
+        <v>1.9352</v>
       </c>
       <c r="J222" t="n">
-        <v>37.402</v>
+        <v>38.704</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.61</v>
       </c>
       <c r="I223" t="n">
-        <v>1.1987</v>
+        <v>1.2182</v>
       </c>
       <c r="J223" t="n">
-        <v>23.974</v>
+        <v>24.364</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.37</v>
       </c>
       <c r="I224" t="n">
-        <v>0.8476</v>
+        <v>0.8401</v>
       </c>
       <c r="J224" t="n">
-        <v>16.952</v>
+        <v>16.802</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.32</v>
       </c>
       <c r="I225" t="n">
-        <v>0.7509</v>
+        <v>0.7363</v>
       </c>
       <c r="J225" t="n">
-        <v>15.018</v>
+        <v>14.726</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.11</v>
       </c>
       <c r="I226" t="n">
-        <v>0.2872</v>
+        <v>0.253</v>
       </c>
       <c r="J226" t="n">
-        <v>5.744</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.93</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.0615</v>
+        <v>-0.0432</v>
       </c>
       <c r="J227" t="n">
-        <v>-1.23</v>
+        <v>-0.864</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.82</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.193</v>
+        <v>-0.1772</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.86</v>
+        <v>-3.544</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.8</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2143</v>
+        <v>-0.1993</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.286</v>
+        <v>-3.986</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.42</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5586</v>
+        <v>-0.5643</v>
       </c>
       <c r="J230" t="n">
-        <v>-11.172</v>
+        <v>-11.286</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.32</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6456</v>
+        <v>-0.6659</v>
       </c>
       <c r="J231" t="n">
-        <v>-12.912</v>
+        <v>-13.318</v>
       </c>
     </row>
   </sheetData>
